--- a/BOOKING_RESULT_Milan_08-10-2026_000000_08-15-2026_000000_1_guests.xlsx
+++ b/BOOKING_RESULT_Milan_08-10-2026_000000_08-15-2026_000000_1_guests.xlsx
@@ -19,241 +19,295 @@
     <x:t>HotelName</x:t>
   </x:si>
   <x:si>
-    <x:t>Url</x:t>
+    <x:t>HotelUrl</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rating</x:t>
   </x:si>
   <x:si>
     <x:t>Price</x:t>
   </x:si>
   <x:si>
-    <x:t>Rating</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Central houses budget friendly</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/central-houses-budget-friendly.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1407467402_412519025_0_0_0&amp;highlighted_blocks=1407467402_412519025_0_0_0&amp;matching_block_id=1407467402_412519025_0_0_0&amp;sr_pri_blocks=1407467402_412519025_0_0_0__70206&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>702 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>YamaLuxe Luxury Apartments - București</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/yamaluxe-apartments-bucuresti.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1171951105_389727277_2_2_0&amp;highlighted_blocks=1171951105_389727277_2_2_0&amp;matching_block_id=1171951105_389727277_2_2_0&amp;sr_pri_blocks=1171951105_389727277_2_2_0__61435&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t/>
+    <x:t>https://www.booking.com/hotel/ro/white-residence-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=559451708_209413944_0_0_0&amp;highlighted_blocks=559451708_209413944_0_0_0&amp;matching_block_id=559451708_209413944_0_0_0&amp;sr_pri_blocks=559451708_209413944_0_0_0__1537547&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MGI studio CORESI &amp; parking</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,375 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11,193 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bark Inn - Bed and Breakfast</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/bark-inn-bed-and-breakfast.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1320902003_404782112_0_1_0&amp;highlighted_blocks=1320902003_404782112_0_1_0&amp;matching_block_id=1320902003_404782112_0_1_0&amp;sr_pri_blocks=1320902003_404782112_0_1_0__3046050&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51,879 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Apartament Racadau</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/apartament-racadau-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=749019701_331158284_3_0_0&amp;highlighted_blocks=749019701_331158284_3_0_0&amp;matching_block_id=749019701_331158284_3_0_0&amp;sr_pri_blocks=749019701_331158284_3_0_0__1488816&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,279 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Aparthotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-aparthotel-1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=995130006_405288024_4_0_0&amp;highlighted_blocks=995130006_405288024_4_0_0&amp;matching_block_id=995130006_405288024_4_0_0&amp;sr_pri_blocks=995130006_405288024_4_0_0__3084939&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Select City Center Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/historical-center-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=31850708_421755992_3_0_0&amp;highlighted_blocks=31850708_421755992_3_0_0&amp;matching_block_id=31850708_421755992_3_0_0&amp;sr_pri_blocks=31850708_421755992_3_0_0__2585682&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,857 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36,050 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pension Bavaria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pension-bavaria.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=31458704_246256401_3_0_0&amp;highlighted_blocks=31458704_246256401_3_0_0&amp;matching_block_id=31458704_246256401_3_0_0&amp;sr_pri_blocks=31458704_246256401_3_0_0__1971000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,710 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73,128 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TampaView ApartHotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/tampaview-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1422457001_423999646_0_0_0&amp;highlighted_blocks=1422457001_423999646_0_0_0&amp;matching_block_id=1422457001_423999646_0_0_0&amp;sr_pri_blocks=1422457001_423999646_0_0_0__3605000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Luca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/luca-brasov2.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1348675301_408707859_0_0_0&amp;highlighted_blocks=1348675301_408707859_0_0_0&amp;matching_block_id=1348675301_408707859_0_0_0&amp;sr_pri_blocks=1348675301_408707859_0_0_0__1287000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,870 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,853 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Davino Aparthotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-davino-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1094405206_382349208_4_0_0_877326&amp;highlighted_blocks=1094405206_382349208_4_0_0_877326&amp;matching_block_id=1094405206_382349208_4_0_0_877326&amp;sr_pri_blocks=1094405206_382349208_4_0_0_877326_2571956&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,720 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Nest</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-nest-brasov20.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1324188501_425784292_4_0_0&amp;highlighted_blocks=1324188501_425784292_4_0_0&amp;matching_block_id=1324188501_425784292_4_0_0&amp;sr_pri_blocks=1324188501_425784292_4_0_0__4051944&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAD Luxury Apartments Kasper</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/jad-confortable-promenada-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1109165407_383666009_3_0_0_337045&amp;highlighted_blocks=1109165407_383666009_3_0_0_337045&amp;matching_block_id=1109165407_383666009_3_0_0_337045&amp;sr_pri_blocks=1109165407_383666009_3_0_0_337045_2323200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Memo Haus</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/koa-memo-haus.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1395631202_411470735_4_0_0&amp;highlighted_blocks=1395631202_411470735_4_0_0&amp;matching_block_id=1395631202_411470735_4_0_0&amp;sr_pri_blocks=1395631202_411470735_4_0_0__3344279&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,321 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Skylark Central Aparthotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/skylark-geneva-suite-with-fireplace-amp-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1117857507_384637893_3_0_0&amp;highlighted_blocks=1117857507_384637893_3_0_0&amp;matching_block_id=1117857507_384637893_3_0_0&amp;sr_pri_blocks=1117857507_384637893_3_0_0__3465000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34,650 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEAK Aparthotel - Old Town - by CityHost</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/peak-aparthotel-by-cityhost.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1166912003_389307937_3_0_0&amp;highlighted_blocks=1166912003_389307937_3_0_0&amp;matching_block_id=1166912003_389307937_3_0_0&amp;sr_pri_blocks=1166912003_389307937_3_0_0__2975419&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33,044 lei29,754 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JAD Comfortable Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/jad-isaran.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=969942706_369395472_3_0_0_337069&amp;highlighted_blocks=969942706_369395472_3_0_0_337069&amp;matching_block_id=969942706_369395472_3_0_0_337069&amp;sr_pri_blocks=969942706_369395472_3_0_0_337069_2185260&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Casa Roth</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/casa-roth-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=251825904_222711381_3_0_0&amp;highlighted_blocks=251825904_222711381_3_0_0&amp;matching_block_id=251825904_222711381_3_0_0&amp;sr_pri_blocks=251825904_222711381_3_0_0__1927930&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pensiunea Leo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/pensiunea-leo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=34116103_264837064_3_0_0&amp;highlighted_blocks=34116103_264837064_3_0_0&amp;matching_block_id=34116103_264837064_3_0_0&amp;sr_pri_blocks=34116103_264837064_3_0_0__2178000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21,780 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mandala Designer Apartments with Free Private Parking, near Mall Coresi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/mandala-a-designer-penthouse-with-free-private-parking-near-mall-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=929406402_364926508_5_0_0&amp;highlighted_blocks=929406402_364926508_5_0_0&amp;matching_block_id=929406402_364926508_5_0_0&amp;sr_pri_blocks=929406402_364926508_5_0_0__7312800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KOA - Sunlight Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/sunlight-apartment-by-taboo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=806763501_360416925_4_0_0&amp;highlighted_blocks=806763501_360416925_4_0_0&amp;matching_block_id=806763501_360416925_4_0_0&amp;sr_pri_blocks=806763501_360416925_4_0_0__2564430&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,644 lei</x:t>
   </x:si>
   <x:si>
     <x:t>9.0</x:t>
   </x:si>
   <x:si>
-    <x:t>Bucharest Central C Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/old-town-bohemian-attic.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1052035601_399555355_2_0_0&amp;highlighted_blocks=1052035601_399555355_2_0_0&amp;matching_block_id=1052035601_399555355_2_0_0&amp;sr_pri_blocks=1052035601_399555355_2_0_0__62428&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>624 lei</x:t>
+    <x:t>Bb's Cosy Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/bb-39-s-cosy-apartments-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=295908503_329654120_0_0_0&amp;highlighted_blocks=295908503_329654120_0_0_0&amp;matching_block_id=295908503_329654120_0_0_0&amp;sr_pri_blocks=295908503_329654120_0_0_0__2194500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,080 lei21,945 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Warm Amber Suites Brașov</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/cosmopolit-lifestyle.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=282931413_126032420_3_0_0_677855&amp;highlighted_blocks=282931413_126032420_3_0_0_677855&amp;matching_block_id=282931413_126032420_3_0_0_677855&amp;sr_pri_blocks=282931413_126032420_3_0_0_677855_3132080&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coresi Mall Area Studios &amp; Apartments by GLAM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/coresi-mall-area-studios-amp-apartments-by-glam.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1118248102_412223809_3_0_0&amp;highlighted_blocks=1118248102_412223809_3_0_0&amp;matching_block_id=1118248102_412223809_3_0_0&amp;sr_pri_blocks=1118248102_412223809_3_0_0__2877300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,773 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Old Town View &amp; Balcony Apartments MM Host</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/brasov-old-town-with-mountain-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1428222201_417107964_3_0_0&amp;highlighted_blocks=1428222201_417107964_3_0_0&amp;matching_block_id=1428222201_417107964_3_0_0&amp;sr_pri_blocks=1428222201_417107964_3_0_0__5187930&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,993 lei16,263 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Main Square Apartments &amp; More</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/main-square-apartments-amp-more.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=116190210_208743329_0_0_0&amp;highlighted_blocks=116190210_208743329_0_0_0&amp;matching_block_id=116190210_208743329_0_0_0&amp;sr_pri_blocks=116190210_208743329_0_0_0__1626341&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Città Studi Suites - Top Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bb-too-cute-2b-str8.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKRoarKBsACAdICJDZmMGU5Mzc2LTJjYjgtNGRiMy05NWI0LWRhYmUwZjRkYzUzYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=26&amp;hapos=26&amp;sr_order=popularity&amp;srpvid=d0bf5a9436ca15d7&amp;srepoch=1766494379&amp;all_sr_blocks=120214214_373646928_1_0_0&amp;highlighted_blocks=120214214_373646928_1_0_0&amp;matching_block_id=120214214_373646928_1_0_0&amp;sr_pri_blocks=120214214_373646928_1_0_0__43850&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>8.9</x:t>
   </x:si>
   <x:si>
-    <x:t>Piața Romană Zone Apartament</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/piata-romana-zone-apartament.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1517819701_423491097_2_0_0&amp;highlighted_blocks=1517819701_423491097_2_0_0&amp;matching_block_id=1517819701_423491097_2_0_0&amp;sr_pri_blocks=1517819701_423491097_2_0_0__59700&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>The City Retreat Apart-Hotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/the-city-retreat-apart.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1332711703_405777882_2_0_0_913798&amp;highlighted_blocks=1332711703_405777882_2_0_0_913798&amp;matching_block_id=1332711703_405777882_2_0_0_913798&amp;sr_pri_blocks=1332711703_405777882_2_0_0_913798_76837&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>768 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Old City Calea Victoriei Deluxe</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/old-city-calea-victoriei-deluxe.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1504909701_422237916_2_0_0&amp;highlighted_blocks=1504909701_422237916_2_0_0&amp;matching_block_id=1504909701_422237916_2_0_0&amp;sr_pri_blocks=1504909701_422237916_2_0_0__76150&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Home Guest - Apartment 3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/home-guest-apartments-bucuresti1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1385508701_414901259_2_0_0&amp;highlighted_blocks=1385508701_414901259_2_0_0&amp;matching_block_id=1385508701_414901259_2_0_0&amp;sr_pri_blocks=1385508701_414901259_2_0_0__45900&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Central Residence Apartment 812 B3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/central-residence-apartment-812.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1144452501_387298811_2_0_0_561427&amp;highlighted_blocks=1144452501_387298811_2_0_0_561427&amp;matching_block_id=1144452501_387298811_2_0_0_561427&amp;sr_pri_blocks=1144452501_387298811_2_0_0_561427_62000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>620 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Arena Park</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/arena-park.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1392496305_411201441_2_0_0_1164546&amp;highlighted_blocks=1392496305_411201441_2_0_0_1164546&amp;matching_block_id=1392496305_411201441_2_0_0_1164546&amp;sr_pri_blocks=1392496305_411201441_2_0_0_1164546_67500&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Central Residence Studio P25</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/central-residence-studio-p25.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1268463001_399568933_2_0_0_603269&amp;highlighted_blocks=1268463001_399568933_2_0_0_603269&amp;matching_block_id=1268463001_399568933_2_0_0_603269&amp;sr_pri_blocks=1268463001_399568933_2_0_0_603269_62000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AT Central Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/at-central-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=503858904_408972632_2_0_0_521942&amp;highlighted_blocks=503858904_408972632_2_0_0_521942&amp;matching_block_id=503858904_408972632_2_0_0_521942&amp;sr_pri_blocks=503858904_408972632_2_0_0_521942_96000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>960 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pura Vida Downtown Tiny houses</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/downtown-tiny-houses-near-cismigiu-gardens.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1289267905_401875389_2_0_0_750797&amp;highlighted_blocks=1289267905_401875389_2_0_0_750797&amp;matching_block_id=1289267905_401875389_2_0_0_750797&amp;sr_pri_blocks=1289267905_401875389_2_0_0_750797_57335&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>573 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Upground Residence Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/upground-residence-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=460874901_0_2_0_0&amp;highlighted_blocks=460874901_0_2_0_0&amp;matching_block_id=460874901_0_2_0_0&amp;sr_pri_blocks=460874901_0_2_0_0__84302&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>365 Apartments in Bucharest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/365-apartments-in-bucharest.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1089796301_381884070_2_0_0&amp;highlighted_blocks=1089796301_381884070_2_0_0&amp;matching_block_id=1089796301_381884070_2_0_0&amp;sr_pri_blocks=1089796301_381884070_2_0_0__121784&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Riviera Unirii Residence</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/riviera-unirii-residence.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=927007703_383045109_0_2_0&amp;highlighted_blocks=927007703_383045109_0_2_0&amp;matching_block_id=927007703_383045109_0_2_0&amp;sr_pri_blocks=927007703_383045109_0_2_0__57000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Crystal Palace Hotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/crystal-palace.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=4116105_141318468_2_2_0_590627&amp;highlighted_blocks=4116105_141318468_2_2_0_590627&amp;matching_block_id=4116105_141318468_2_2_0_590627&amp;sr_pri_blocks=4116105_141318468_2_2_0_590627_167642&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Ultimate Living Experience - Modern Accommodation &amp; Free Parking near Romexpo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/two-bedroom-apartment-with-free-parking.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=769352802_334675763_2_0_0&amp;highlighted_blocks=769352802_334675763_2_0_0&amp;matching_block_id=769352802_334675763_2_0_0&amp;sr_pri_blocks=769352802_334675763_2_0_0__93670&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>937 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HIGHLINE DOWNTOWN ApartHotel OLDTOWN UNIRII SQUARE</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/highline-downtown.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=550833714_200909667_2_0_0&amp;highlighted_blocks=550833714_200909667_2_0_0&amp;matching_block_id=550833714_200909667_2_0_0&amp;sr_pri_blocks=550833714_200909667_2_0_0__104438&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,044 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Downtown Terrace Nest Victoriei Gara de Nord</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/downtown-terrace-nest-victory-gara-de-nord.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1470621701_418410430_2_0_0&amp;highlighted_blocks=1470621701_418410430_2_0_0&amp;matching_block_id=1470621701_418410430_2_0_0&amp;sr_pri_blocks=1470621701_418410430_2_0_0__173400&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>One by One - by Grand Accommodation</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bucharest-check-in.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=224642942_413845015_2_0_0&amp;highlighted_blocks=224642942_413845015_2_0_0&amp;matching_block_id=224642942_413845015_2_0_0&amp;sr_pri_blocks=224642942_413845015_2_0_0__108000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Wonderful Apartments in Prime North Location - Heaven for Extended Stays</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/wonderful-1br-amp-balcony-heaven-for-extended-stays.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1061440001_378456007_2_0_0&amp;highlighted_blocks=1061440001_378456007_2_0_0&amp;matching_block_id=1061440001_378456007_2_0_0&amp;sr_pri_blocks=1061440001_378456007_2_0_0__124270&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1,243 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bright and cozy apartment in the Bucharest center</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bright-and-cozy-apartment-in-the-bucharest-center.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1357898201_408129470_2_0_0&amp;highlighted_blocks=1357898201_408129470_2_0_0&amp;matching_block_id=1357898201_408129470_2_0_0&amp;sr_pri_blocks=1357898201_408129470_2_0_0__58320&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Tomis Garden Bucuresti</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/tomis-garden-bucuresti.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__137193&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bucharest Premium Luxury Studios &amp; Apartments by Glam Story</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bucharest-premium-luxury-studios-amp-apartments-by-glam-story.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=1337095501_412223728_2_0_0&amp;highlighted_blocks=1337095501_412223728_2_0_0&amp;matching_block_id=1337095501_412223728_2_0_0&amp;sr_pri_blocks=1337095501_412223728_2_0_0__110000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ROSETTI Hotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/rosetti-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALrrKDKBsACAdICJDNkMWFmYTZkLWJhN2UtNDE5MS04NmIwLTAxNjk5OTM2NmQzMNgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-01-07&amp;checkout=2026-01-10&amp;dest_id=-1153951&amp;dest_type=city&amp;group_adults=2&amp;req_adults=2&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;srpvid=0ceb08b791caef551c458d027f082fe5&amp;srepoch=1766488807&amp;all_sr_blocks=0_0_2_0_0&amp;highlighted_blocks=0_0_2_0_0&amp;matching_block_id=0_0_2_0_0&amp;sr_pri_blocks=0_0_2_0_0__122275&amp;from=searchresults</x:t>
+    <x:t>2,231 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brasov Gondola Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/ro/mgi-studio-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1413131701_413051882_0_0_0&amp;highlighted_blocks=1413131701_413051882_0_0_0&amp;matching_block_id=1413131701_413051882_0_0_0&amp;sr_pri_blocks=1413131701_413051882_0_0_0__1119300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,461 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,888 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,849 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,519 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23,232 lei</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33,443 lei</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -604,7 +658,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:D26"/>
+  <x:dimension ref="A1:C26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -623,128 +677,128 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B2" s="0" t="s">
-        <x:v>5</x:v>
-      </x:c>
       <x:c r="C2" s="0" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D2" s="0" t="s">
         <x:v>6</x:v>
-      </x:c>
-      <x:c r="D2" s="0" t="s">
-        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
+        <x:v>5</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="C3" s="0" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="C3" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>13</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>14</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>92</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>17</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>93</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="C6" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C6" s="0" t="s">
-        <x:v>21</x:v>
-      </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>94</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C8" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="D8" s="0" t="s">
         <x:v>26</x:v>
-      </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D8" s="0" t="s">
-        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="B9" s="0" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="B9" s="0" t="s">
+      <x:c r="C9" s="0" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="C9" s="0" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="B10" s="0" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C10" s="0" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="D10" s="0" t="s">
         <x:v>33</x:v>
-      </x:c>
-      <x:c r="B10" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-      <x:c r="C10" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D10" s="0" t="s">
-        <x:v>25</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
@@ -755,24 +809,24 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>37</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>95</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
@@ -786,7 +840,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>96</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
@@ -797,178 +851,192 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>97</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>34</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>48</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>18</x:v>
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:4">
+      <x:c r="A27" s="0" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="B27" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>89</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/BOOKING_RESULT_Milan_08-10-2026_000000_08-15-2026_000000_1_guests.xlsx
+++ b/BOOKING_RESULT_Milan_08-10-2026_000000_08-15-2026_000000_1_guests.xlsx
@@ -28,286 +28,1828 @@
     <x:t>Price</x:t>
   </x:si>
   <x:si>
-    <x:t>https://www.booking.com/hotel/ro/white-residence-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=559451708_209413944_0_0_0&amp;highlighted_blocks=559451708_209413944_0_0_0&amp;matching_block_id=559451708_209413944_0_0_0&amp;sr_pri_blocks=559451708_209413944_0_0_0__1537547&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MGI studio CORESI &amp; parking</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,375 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11,193 lei</x:t>
+    <x:t>https://www.booking.com/hotel/it/loft-di-design-a-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=1&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=1311383501_406725388_2_0_0&amp;highlighted_blocks=1311383501_406725388_2_0_0&amp;matching_block_id=1311383501_406725388_2_0_0&amp;sr_pri_blocks=1311383501_406725388_2_0_0__68743&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/unahotels-galles-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8075437_88434879_1_2_0_815692&amp;highlighted_blocks=8075437_88434879_1_2_0_815692&amp;matching_block_id=8075437_88434879_1_2_0_815692&amp;sr_pri_blocks=8075437_88434879_1_2_0_815692_43760&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t/>
+  </x:si>
+  <x:si>
+    <x:t>UNA Hotels Galles Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hostel-inn-petrella.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=1496723205_421348607_1_2_0&amp;highlighted_blocks=1496723205_421348607_1_2_0&amp;matching_block_id=1496723205_421348607_1_2_0&amp;sr_pri_blocks=1496723205_421348607_1_2_0__26500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,226</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hostel INN PETRELLA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ripamonti-milan-navigli.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=1164909503_396081722_0_0_0&amp;highlighted_blocks=1164909503_396081722_0_0_0&amp;matching_block_id=1164909503_396081722_0_0_0&amp;sr_pri_blocks=1164909503_396081722_0_0_0__31000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,348</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aparto Milan Ripamonti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/qualys-hotel-nasco.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8105812_92524515_1_1_0&amp;highlighted_blocks=8105812_92524515_1_1_0&amp;matching_block_id=8105812_92524515_1_1_0&amp;sr_pri_blocks=8105812_92524515_1_1_0__46400&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,577</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Nasco</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelmozartmilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8137101_94109344_0_2_0&amp;highlighted_blocks=8137101_94109344_0_2_0&amp;matching_block_id=8137101_94109344_0_2_0&amp;sr_pri_blocks=8137101_94109344_0_2_0__44992&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,360</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Mozart</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bandb-hotel-milano-ornato.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8510442_91462511_1_2_0&amp;highlighted_blocks=8510442_91462511_1_2_0&amp;matching_block_id=8510442_91462511_1_2_0&amp;sr_pri_blocks=8510442_91462511_1_2_0__31199&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B&amp;B HOTEL Milano Ornato</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/meininger-milano-garibaldi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=271668605_106261093_0_2_0_496217&amp;highlighted_blocks=271668605_106261093_0_2_0_496217&amp;matching_block_id=271668605_106261093_0_2_0_496217&amp;sr_pri_blocks=271668605_106261093_0_2_0_496217_17250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,587</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEININGER Milano Garibaldi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelmarzomilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8095101_114805712_0_0_0&amp;highlighted_blocks=8095101_114805712_0_0_0&amp;matching_block_id=8095101_114805712_0_0_0&amp;sr_pri_blocks=8095101_114805712_0_0_0__39167&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>878</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel 22 Marzo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/biocity.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=39903701_404373992_0_2_0&amp;highlighted_blocks=39903701_404373992_0_2_0&amp;matching_block_id=39903701_404373992_0_2_0&amp;sr_pri_blocks=39903701_404373992_0_2_0__46700&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>9.3</x:t>
   </x:si>
   <x:si>
-    <x:t>Bark Inn - Bed and Breakfast</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bark-inn-bed-and-breakfast.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=3&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1320902003_404782112_0_1_0&amp;highlighted_blocks=1320902003_404782112_0_1_0&amp;matching_block_id=1320902003_404782112_0_1_0&amp;sr_pri_blocks=1320902003_404782112_0_1_0__3046050&amp;from=searchresults</x:t>
+    <x:t>1,993</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Biocity</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ibismilanocentromilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8140407_94296350_1_34_0&amp;highlighted_blocks=8140407_94296350_1_34_0&amp;matching_block_id=8140407_94296350_1_34_0&amp;sr_pri_blocks=8140407_94296350_1_34_0__41906&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,376</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ibis Milano Centro</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/garda.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8485201_379775033_0_2_0&amp;highlighted_blocks=8485201_379775033_0_2_0&amp;matching_block_id=8485201_379775033_0_2_0&amp;sr_pri_blocks=8485201_379775033_0_2_0__43700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,132</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Garda</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brianza.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8906203_386846277_0_1_0&amp;highlighted_blocks=8906203_386846277_0_1_0&amp;matching_block_id=8906203_386846277_0_1_0&amp;sr_pri_blocks=8906203_386846277_0_1_0__45100&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Brianza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residence-lepontina.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=27200801_88154757_0_0_0&amp;highlighted_blocks=27200801_88154757_0_0_0&amp;matching_block_id=27200801_88154757_0_0_0&amp;sr_pri_blocks=27200801_88154757_0_0_0__34300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,294</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residence Lepontina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/21-house-of-stories-citta-studi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=521990401_182686817_1_1_0&amp;highlighted_blocks=521990401_182686817_1_1_0&amp;matching_block_id=521990401_182686817_1_1_0&amp;sr_pri_blocks=521990401_182686817_1_1_0__54730&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,745</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21 House of Stories Città Studi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/koala-hostel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=115765503_89378560_0_0_0&amp;highlighted_blocks=115765503_89378560_0_0_0&amp;matching_block_id=115765503_89378560_0_0_0&amp;sr_pri_blocks=115765503_89378560_0_0_0__11285&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,784</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Koala Hostel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AH - Collezione Brera</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.4</x:t>
+  </x:si>
+  <x:si>
+    <x:t>574</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ah-collezione-brera.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=1533159102_424847158_2_2_0&amp;highlighted_blocks=1533159102_424847158_2_2_0&amp;matching_block_id=1533159102_424847158_2_2_0&amp;sr_pri_blocks=1533159102_424847158_2_2_0__156402&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,957</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Oasi Village Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/oasi-village.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=32221701_88456068_0_2_0&amp;highlighted_blocks=32221701_88456068_0_2_0&amp;matching_block_id=32221701_88456068_0_2_0&amp;sr_pri_blocks=32221701_88456068_0_2_0__37076&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,886</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Amedia Hotel Milan, Trademark Collection by Wyndham</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/amedia-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=717918007_299189387_1_1_0&amp;highlighted_blocks=717918007_299189387_1_1_0&amp;matching_block_id=717918007_299189387_1_1_0&amp;sr_pri_blocks=717918007_299189387_1_1_0__49900&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,291</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,539</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Calimala Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/calimala-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=1288322001_401781036_1_2_0&amp;highlighted_blocks=1288322001_401781036_1_2_0&amp;matching_block_id=1288322001_401781036_1_2_0&amp;sr_pri_blocks=1288322001_401781036_1_2_0__104000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bovisa Urban Garden</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/abcd-ap.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=1165812802_389236709_0_0_0_663459&amp;highlighted_blocks=1165812802_389236709_0_0_0_663459&amp;matching_block_id=1165812802_389236709_0_0_0_663459&amp;sr_pri_blocks=1165812802_389236709_0_0_0_663459_18060&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>919</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Golden Milano Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/golden-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=410152401_125150024_0_2_0&amp;highlighted_blocks=410152401_125150024_0_2_0&amp;matching_block_id=410152401_125150024_0_2_0&amp;sr_pri_blocks=410152401_125150024_0_2_0__37450&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,905</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Babila Hostel &amp; Bistrot</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/babila-hostel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=235295909_100982359_0_2_0_663414&amp;highlighted_blocks=235295909_100982359_0_2_0_663414&amp;matching_block_id=235295909_100982359_0_2_0_663414&amp;sr_pri_blocks=235295909_100982359_0_2_0_663414_22843&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Sanpi Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelsanpimilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8065201_93707714_0_2_0&amp;highlighted_blocks=8065201_93707714_0_2_0&amp;matching_block_id=8065201_93707714_0_2_0&amp;sr_pri_blocks=8065201_93707714_0_2_0__62300&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Campion CityLife</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/campion.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=27461904_407235448_0_1_0&amp;highlighted_blocks=27461904_407235448_0_1_0&amp;matching_block_id=27461904_407235448_0_1_0&amp;sr_pri_blocks=27461904_407235448_0_1_0__53700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,732</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Venini</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Fantastic Flat Famagosta Area, Forum, Parking, Netflix</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/venini-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=26&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=23747103_88162908_0_1_0&amp;highlighted_blocks=23747103_88162908_0_1_0&amp;matching_block_id=23747103_88162908_0_1_0&amp;sr_pri_blocks=23747103_88162908_0_1_0__31700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,613</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Art Hotel Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/art-hotel-navigli.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=27&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=8008305_419546948_0_2_0&amp;highlighted_blocks=8008305_419546948_0_2_0&amp;matching_block_id=8008305_419546948_0_2_0&amp;sr_pri_blocks=8008305_419546948_0_2_0__67625&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel degli Arcimboldi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotel-degli-arcimboldi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=28&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=87220405_88472721_1_2_0&amp;highlighted_blocks=87220405_88472721_1_2_0&amp;matching_block_id=87220405_88472721_1_2_0&amp;sr_pri_blocks=87220405_88472721_1_2_0__40955&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,083</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Vecchia Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/vecchia-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=29&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=29148902_88453544_0_1_0&amp;highlighted_blocks=29148902_88453544_0_1_0&amp;matching_block_id=29148902_88453544_0_1_0&amp;sr_pri_blocks=29148902_88453544_0_1_0__43795&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NYX Hotel Milan by Leonardo Hotels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nyx-milan.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=30&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=205908304_95072706_0_2_0&amp;highlighted_blocks=205908304_95072706_0_2_0&amp;matching_block_id=205908304_95072706_0_2_0&amp;sr_pri_blocks=205908304_95072706_0_2_0__72050&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.6</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,665</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Panda Hostel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/panda-hostel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=31&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=151017904_88480534_0_0_0&amp;highlighted_blocks=151017904_88480534_0_0_0&amp;matching_block_id=151017904_88480534_0_0_0&amp;sr_pri_blocks=151017904_88480534_0_0_0__11800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Minerva</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/minerva-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=32&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=24816202_88450325_0_1_0&amp;highlighted_blocks=24816202_88450325_0_1_0&amp;matching_block_id=24816202_88450325_0_1_0&amp;sr_pri_blocks=24816202_88450325_0_1_0__43525&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,214</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Combo Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/combo-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=33&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=524886302_184243990_0_2_0&amp;highlighted_blocks=524886302_184243990_0_2_0&amp;matching_block_id=524886302_184243990_0_2_0&amp;sr_pri_blocks=524886302_184243990_0_2_0__22323&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,136</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Acca Palace - AA Hotels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/acca-palace.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=34&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=23893910_88163042_0_2_0_1292543&amp;highlighted_blocks=23893910_88163042_0_2_0_1292543&amp;matching_block_id=23893910_88163042_0_2_0_1292543&amp;sr_pri_blocks=23893910_88163042_0_2_0_1292543_62000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,154</x:t>
+  </x:si>
+  <x:si>
+    <x:t>iQ Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/iq-hotel-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=35&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=8120810_91907075_2_2_0&amp;highlighted_blocks=8120810_91907075_2_2_0&amp;matching_block_id=8120810_91907075_2_2_0&amp;sr_pri_blocks=8120810_91907075_2_2_0__81496&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,146</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Bonola</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelbonolamilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=36&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=8110801_88156294_0_2_0&amp;highlighted_blocks=8110801_88156294_0_2_0&amp;matching_block_id=8110801_88156294_0_2_0&amp;sr_pri_blocks=8110801_88156294_0_2_0__25000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carlo Goldoni Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/carlo-goldoni.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=37&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=295560302_109912007_0_2_0&amp;highlighted_blocks=295560302_109912007_0_2_0&amp;matching_block_id=295560302_109912007_0_2_0&amp;sr_pri_blocks=295560302_109912007_0_2_0__36250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,844</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Metrò</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/metro-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=38&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=24570601_363528624_0_1_0&amp;highlighted_blocks=24570601_363528624_0_1_0&amp;matching_block_id=24570601_363528624_0_1_0&amp;sr_pri_blocks=24570601_363528624_0_1_0__58700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,986</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Doria Grand Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/doriagrand.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=39&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=8002301_88152857_0_1_0_1188358&amp;highlighted_blocks=8002301_88152857_0_1_0_1188358&amp;matching_block_id=8002301_88152857_0_1_0_1188358&amp;sr_pri_blocks=8002301_88152857_0_1_0_1188358_62150&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Well-located Campus Rooms Near City Park</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/stylish-units-near-bosco-verticale.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=40&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=1219471903_394113176_0_0_0_1282905&amp;highlighted_blocks=1219471903_394113176_0_0_0_1282905&amp;matching_block_id=1219471903_394113176_0_0_0_1282905&amp;sr_pri_blocks=1219471903_394113176_0_0_0_1282905_49744&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,531</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel MM Dateo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hoteldateo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=41&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=8300601_362644073_0_2_0_1215113&amp;highlighted_blocks=8300601_362644073_0_2_0_1215113&amp;matching_block_id=8300601_362644073_0_2_0_1215113&amp;sr_pri_blocks=8300601_362644073_0_2_0_1215113_29381&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.7</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,495</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Taddei 14C - Washington</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-monolocale-zona-washington.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=42&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=727243102_342454710_0_0_0&amp;highlighted_blocks=727243102_342454710_0_0_0&amp;matching_block_id=727243102_342454710_0_0_0&amp;sr_pri_blocks=727243102_342454710_0_0_0__38690&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,968</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Manin</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/gthotelmanin.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=43&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=8020501_88153066_1_2_0&amp;highlighted_blocks=8020501_88153066_1_2_0&amp;matching_block_id=8020501_88153066_1_2_0&amp;sr_pri_blocks=8020501_88153066_1_2_0__104261&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J24 Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/j24-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=44&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=446233402_134143057_0_2_0&amp;highlighted_blocks=446233402_134143057_0_2_0&amp;matching_block_id=446233402_134143057_0_2_0&amp;sr_pri_blocks=446233402_134143057_0_2_0__45455&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,312</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B&amp;B Sant'Agostino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/b-amp-b-sant-agostino.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=45&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=64942204_366471835_0_1_0&amp;highlighted_blocks=64942204_366471835_0_1_0&amp;matching_block_id=64942204_366471835_0_1_0&amp;sr_pri_blocks=64942204_366471835_0_1_0__46750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,378</x:t>
+  </x:si>
+  <x:si>
+    <x:t>QC Room Milano Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/d-este-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=46&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=38354413_424461271_1_0_0&amp;highlighted_blocks=38354413_424461271_1_0_0&amp;matching_block_id=38354413_424461271_1_0_0&amp;sr_pri_blocks=38354413_424461271_1_0_0__71150&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,620</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hilton Garden Inn Milan North</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hilton-garden-inn-milan-north.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=47&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=135263801_94590342_1_2_0_931769&amp;highlighted_blocks=135263801_94590342_1_2_0_931769&amp;matching_block_id=135263801_94590342_1_2_0_931769&amp;sr_pri_blocks=135263801_94590342_1_2_0_931769_59640&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,034</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Berna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelbernamilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=48&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=8086014_109188047_0_0_0&amp;highlighted_blocks=8086014_109188047_0_0_0&amp;matching_block_id=8086014_109188047_0_0_0&amp;sr_pri_blocks=8086014_109188047_0_0_0__52500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,671</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Spice Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/amadeus.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=49&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=8052201_88153588_0_2_0&amp;highlighted_blocks=8052201_88153588_0_2_0&amp;matching_block_id=8052201_88153588_0_2_0&amp;sr_pri_blocks=8052201_88153588_0_2_0__48655&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,475</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Teco</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelteco.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=50&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896573&amp;all_sr_blocks=8058211_88153635_1_2_0&amp;highlighted_blocks=8058211_88153635_1_2_0&amp;matching_block_id=8058211_88153635_1_2_0&amp;sr_pri_blocks=8058211_88153635_1_2_0__58416&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,972</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Palazzo Quantum 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/palazzo-quantum-1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=51&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=1187317004_391089422_1_0_0&amp;highlighted_blocks=1187317004_391089422_1_0_0&amp;matching_block_id=1187317004_391089422_1_0_0&amp;sr_pri_blocks=1187317004_391089422_1_0_0__44763&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,277</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Glam Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/glam-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=52&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=137910515_88479579_0_2_0&amp;highlighted_blocks=137910515_88479579_0_2_0&amp;matching_block_id=137910515_88479579_0_2_0&amp;sr_pri_blocks=137910515_88479579_0_2_0__67955&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,457</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Berlino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelberlinomilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=53&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=8077910_88054177_0_2_0&amp;highlighted_blocks=8077910_88054177_0_2_0&amp;matching_block_id=8077910_88054177_0_2_0&amp;sr_pri_blocks=8077910_88054177_0_2_0__35200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,791</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Guest House Pirelli Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/guest-house-pirelli-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=54&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=115765704_88477159_0_2_0&amp;highlighted_blocks=115765704_88477159_0_2_0&amp;matching_block_id=115765704_88477159_0_2_0&amp;sr_pri_blocks=115765704_88477159_0_2_0__32250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.5</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,641</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Le Texture Premium Rooms Duomo-Cordusio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/le-texture-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=55&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=476505813_229172089_2_0_0&amp;highlighted_blocks=476505813_229172089_2_0_0&amp;matching_block_id=476505813_229172089_2_0_0&amp;sr_pri_blocks=476505813_229172089_2_0_0__68750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,497</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CSI Group - Hotel Metropoli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/metropoli.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=56&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=708210401_295658148_0_2_0&amp;highlighted_blocks=708210401_295658148_0_2_0&amp;matching_block_id=708210401_295658148_0_2_0&amp;sr_pri_blocks=708210401_295658148_0_2_0__45010&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,290</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7BA Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/7ba-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=57&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=1441135101_415559263_1_2_0&amp;highlighted_blocks=1441135101_415559263_1_2_0&amp;matching_block_id=1441135101_415559263_1_2_0&amp;sr_pri_blocks=1441135101_415559263_1_2_0__63455&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Folen</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/folen.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=58&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=665194601_279313805_0_1_0_1162835&amp;highlighted_blocks=665194601_279313805_0_1_0_1162835&amp;matching_block_id=665194601_279313805_0_1_0_1162835&amp;sr_pri_blocks=665194601_279313805_0_1_0_1162835_67415&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,430</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Lido</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotellidomilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=59&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=8084502_88153892_0_1_0&amp;highlighted_blocks=8084502_88153892_0_1_0&amp;matching_block_id=8084502_88153892_0_1_0&amp;sr_pri_blocks=8084502_88153892_0_1_0__39200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>YellowSquare Milan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/yellowsquare-milan.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=60&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=615523605_240583119_0_0_0_1093603&amp;highlighted_blocks=615523605_240583119_0_0_0_1093603&amp;matching_block_id=615523605_240583119_0_0_0_1093603&amp;sr_pri_blocks=615523605_240583119_0_0_0_1093603_24082&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,225</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lion University &amp; Youth Hostel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/lion-hostel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=61&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=208415006_95528851_0_0_0&amp;highlighted_blocks=208415006_95528851_0_0_0&amp;matching_block_id=208415006_95528851_0_0_0&amp;sr_pri_blocks=208415006_95528851_0_0_0__19500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>992</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Tocq</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotel-tocq.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=62&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=8311203_93707951_1_2_0&amp;highlighted_blocks=8311203_93707951_1_2_0&amp;matching_block_id=8311203_93707951_1_2_0&amp;sr_pri_blocks=8311203_93707951_1_2_0__90425&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WorldHotel Casati 18</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelfelicecasatimilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=63&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=8156011_94109382_2_2_0&amp;highlighted_blocks=8156011_94109382_2_2_0&amp;matching_block_id=8156011_94109382_2_2_0&amp;sr_pri_blocks=8156011_94109382_2_2_0__79437&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>9.2</x:t>
   </x:si>
   <x:si>
-    <x:t>51,879 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Apartament Racadau</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/apartament-racadau-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=4&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=749019701_331158284_3_0_0&amp;highlighted_blocks=749019701_331158284_3_0_0&amp;matching_block_id=749019701_331158284_3_0_0&amp;sr_pri_blocks=749019701_331158284_3_0_0__1488816&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.8</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19,279 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Aparthotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/koa-aparthotel-1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=5&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=995130006_405288024_4_0_0&amp;highlighted_blocks=995130006_405288024_4_0_0&amp;matching_block_id=995130006_405288024_4_0_0&amp;sr_pri_blocks=995130006_405288024_4_0_0__3084939&amp;from=searchresults</x:t>
+    <x:t>4,041</x:t>
+  </x:si>
+  <x:si>
+    <x:t>a&amp;o Hostel Milano Ca Granda</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelibismilanocagranda.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=64&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=8144811_94296638_0_2_0&amp;highlighted_blocks=8144811_94296638_0_2_0&amp;matching_block_id=8144811_94296638_0_2_0&amp;sr_pri_blocks=8144811_94296638_0_2_0__36043&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,834</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milano Verticale | UNA Esperienze</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-verticale-una.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=65&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=8166311_88919989_2_2_0_779363&amp;highlighted_blocks=8166311_88919989_2_2_0_779363&amp;matching_block_id=8166311_88919989_2_2_0_779363&amp;sr_pri_blocks=8166311_88919989_2_2_0_779363_101475&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Holiday Inn Milan Garibaldi Station by IHG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milan-garibaldi-station.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=66&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=2776812_95151786_1_2_0&amp;highlighted_blocks=2776812_95151786_1_2_0&amp;matching_block_id=2776812_95151786_1_2_0&amp;sr_pri_blocks=2776812_95151786_1_2_0__60500&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,078</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Mercurio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mercurio-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=67&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=25025002_88164395_0_2_0&amp;highlighted_blocks=25025002_88164395_0_2_0&amp;matching_block_id=25025002_88164395_0_2_0&amp;sr_pri_blocks=25025002_88164395_0_2_0__27500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.0</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,399</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Starhotels Ritz</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelritz.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=68&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=18702_102656203_1_2_0&amp;highlighted_blocks=18702_102656203_1_2_0&amp;matching_block_id=18702_102656203_1_2_0&amp;sr_pri_blocks=18702_102656203_1_2_0__70000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,561</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AXYHOTELS InnStyle Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/axyhotels-innstyle-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=69&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=8426013_88920388_1_2_0_623440&amp;highlighted_blocks=8426013_88920388_1_2_0_623440&amp;matching_block_id=8426013_88920388_1_2_0_623440&amp;sr_pri_blocks=8426013_88920388_1_2_0_623440_86000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,375</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Kira Suites Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/kira-suites-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=70&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=1443365401_415777282_1_2_0&amp;highlighted_blocks=1443365401_415777282_1_2_0&amp;matching_block_id=1443365401_415777282_1_2_0&amp;sr_pri_blocks=1443365401_415777282_1_2_0__45455&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cadorna Luxury Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cadorna-luxury-milano1234567891011121314151617181920.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=71&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=817709201_344330097_0_0_0&amp;highlighted_blocks=817709201_344330097_0_0_0&amp;matching_block_id=817709201_344330097_0_0_0&amp;sr_pri_blocks=817709201_344330097_0_0_0__62180&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Novi 2 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-penthouse-sui-navigli.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=72&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896574&amp;all_sr_blocks=1073189802_379864802_2_0_0&amp;highlighted_blocks=1073189802_379864802_2_0_0&amp;matching_block_id=1073189802_379864802_2_0_0&amp;sr_pri_blocks=1073189802_379864802_2_0_0__97496&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,960</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Crivi's</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/gtcrivi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=73&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8020208_88153052_0_2_0&amp;highlighted_blocks=8020208_88153052_0_2_0&amp;matching_block_id=8020208_88153052_0_2_0&amp;sr_pri_blocks=8020208_88153052_0_2_0__63926&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,252</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Numa Milan Sempione</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/numa-milan-sempione.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=74&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=1244681402_396582596_1_0_0_1190352&amp;highlighted_blocks=1244681402_396582596_1_0_0_1190352&amp;matching_block_id=1244681402_396582596_1_0_0_1190352&amp;sr_pri_blocks=1244681402_396582596_1_0_0_1190352_52700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,681</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Piacenza</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/piacenza.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=75&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=23589901_88162580_0_1_0&amp;highlighted_blocks=23589901_88162580_0_1_0&amp;matching_block_id=23589901_88162580_0_1_0&amp;sr_pri_blocks=23589901_88162580_0_1_0__50725&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,580</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Dei Fiori</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/dei-fiori.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=76&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8917901_415083514_0_2_0&amp;highlighted_blocks=8917901_415083514_0_2_0&amp;matching_block_id=8917901_415083514_0_2_0&amp;sr_pri_blocks=8917901_415083514_0_2_0__39700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,020</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Da Vinci</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotel-da-vinci.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=77&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8366921_88437169_0_2_0&amp;highlighted_blocks=8366921_88437169_0_2_0&amp;matching_block_id=8366921_88437169_0_2_0&amp;sr_pri_blocks=8366921_88437169_0_2_0__38075&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,937</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BB Hotels Aparthotel Visconti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bb-hotels-aparthotel-visconti.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=78&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=175892501_362128576_2_0_0&amp;highlighted_blocks=175892501_362128576_2_0_0&amp;matching_block_id=175892501_362128576_2_0_0&amp;sr_pri_blocks=175892501_362128576_2_0_0__45250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Milu Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milu-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=79&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=1358770701_408197535_0_2_0&amp;highlighted_blocks=1358770701_408197535_0_2_0&amp;matching_block_id=1358770701_408197535_0_2_0&amp;sr_pri_blocks=1358770701_408197535_0_2_0__101750&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>9.6</x:t>
   </x:si>
   <x:si>
-    <x:t>Select City Center Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/historical-center-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=6&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=31850708_421755992_3_0_0&amp;highlighted_blocks=31850708_421755992_3_0_0&amp;matching_block_id=31850708_421755992_3_0_0&amp;sr_pri_blocks=31850708_421755992_3_0_0__2585682&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,857 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>36,050 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pension Bavaria</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/pension-bavaria.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=7&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=31458704_246256401_3_0_0&amp;highlighted_blocks=31458704_246256401_3_0_0&amp;matching_block_id=31458704_246256401_3_0_0&amp;sr_pri_blocks=31458704_246256401_3_0_0__1971000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19,710 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>73,128 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>TampaView ApartHotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/tampaview-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=8&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1422457001_423999646_0_0_0&amp;highlighted_blocks=1422457001_423999646_0_0_0&amp;matching_block_id=1422457001_423999646_0_0_0&amp;sr_pri_blocks=1422457001_423999646_0_0_0__3605000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Luca</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/luca-brasov2.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=9&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1348675301_408707859_0_0_0&amp;highlighted_blocks=1348675301_408707859_0_0_0&amp;matching_block_id=1348675301_408707859_0_0_0&amp;sr_pri_blocks=1348675301_408707859_0_0_0__1287000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,870 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21,853 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Davino Aparthotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/koa-davino-aparthotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=10&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1094405206_382349208_4_0_0_877326&amp;highlighted_blocks=1094405206_382349208_4_0_0_877326&amp;matching_block_id=1094405206_382349208_4_0_0_877326&amp;sr_pri_blocks=1094405206_382349208_4_0_0_877326_2571956&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,720 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Nest</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/koa-nest-brasov20.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=11&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1324188501_425784292_4_0_0&amp;highlighted_blocks=1324188501_425784292_4_0_0&amp;matching_block_id=1324188501_425784292_4_0_0&amp;sr_pri_blocks=1324188501_425784292_4_0_0__4051944&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.7</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JAD Luxury Apartments Kasper</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/jad-confortable-promenada-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=12&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1109165407_383666009_3_0_0_337045&amp;highlighted_blocks=1109165407_383666009_3_0_0_337045&amp;matching_block_id=1109165407_383666009_3_0_0_337045&amp;sr_pri_blocks=1109165407_383666009_3_0_0_337045_2323200&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Memo Haus</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/koa-memo-haus.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=13&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1395631202_411470735_4_0_0&amp;highlighted_blocks=1395631202_411470735_4_0_0&amp;matching_block_id=1395631202_411470735_4_0_0&amp;sr_pri_blocks=1395631202_411470735_4_0_0__3344279&amp;from=searchresults</x:t>
+    <x:t>5,176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Town Suites</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/town-house-street.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=80&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=1207543301_392944778_1_0_0&amp;highlighted_blocks=1207543301_392944778_1_0_0&amp;matching_block_id=1207543301_392944778_1_0_0&amp;sr_pri_blocks=1207543301_392944778_1_0_0__67603&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,439</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ostello Bello Milano Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ostello-bello.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=81&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=151909517_88753189_0_2_0_1139564&amp;highlighted_blocks=151909517_88753189_0_2_0_1139564&amp;matching_block_id=151909517_88753189_0_2_0_1139564&amp;sr_pri_blocks=151909517_88753189_0_2_0_1139564_27416&amp;from=searchresults</x:t>
   </x:si>
   <x:si>
     <x:t>8.8</x:t>
   </x:si>
   <x:si>
-    <x:t>31,321 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Skylark Central Aparthotel</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/skylark-geneva-suite-with-fireplace-amp-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=14&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1117857507_384637893_3_0_0&amp;highlighted_blocks=1117857507_384637893_3_0_0&amp;matching_block_id=1117857507_384637893_3_0_0&amp;sr_pri_blocks=1117857507_384637893_3_0_0__3465000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>34,650 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PEAK Aparthotel - Old Town - by CityHost</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/peak-aparthotel-by-cityhost.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=15&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1166912003_389307937_3_0_0&amp;highlighted_blocks=1166912003_389307937_3_0_0&amp;matching_block_id=1166912003_389307937_3_0_0&amp;sr_pri_blocks=1166912003_389307937_3_0_0__2975419&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33,044 lei29,754 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JAD Comfortable Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/jad-isaran.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=16&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=969942706_369395472_3_0_0_337069&amp;highlighted_blocks=969942706_369395472_3_0_0_337069&amp;matching_block_id=969942706_369395472_3_0_0_337069&amp;sr_pri_blocks=969942706_369395472_3_0_0_337069_2185260&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.4</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Casa Roth</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/casa-roth-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=17&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=251825904_222711381_3_0_0&amp;highlighted_blocks=251825904_222711381_3_0_0&amp;matching_block_id=251825904_222711381_3_0_0&amp;sr_pri_blocks=251825904_222711381_3_0_0__1927930&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.1</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Pensiunea Leo</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/pensiunea-leo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=18&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=34116103_264837064_3_0_0&amp;highlighted_blocks=34116103_264837064_3_0_0&amp;matching_block_id=34116103_264837064_3_0_0&amp;sr_pri_blocks=34116103_264837064_3_0_0__2178000&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>21,780 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Mandala Designer Apartments with Free Private Parking, near Mall Coresi</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/mandala-a-designer-penthouse-with-free-private-parking-near-mall-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=19&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=929406402_364926508_5_0_0&amp;highlighted_blocks=929406402_364926508_5_0_0&amp;matching_block_id=929406402_364926508_5_0_0&amp;sr_pri_blocks=929406402_364926508_5_0_0__7312800&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KOA - Sunlight Apartment</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/sunlight-apartment-by-taboo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=20&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=806763501_360416925_4_0_0&amp;highlighted_blocks=806763501_360416925_4_0_0&amp;matching_block_id=806763501_360416925_4_0_0&amp;sr_pri_blocks=806763501_360416925_4_0_0__2564430&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,644 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9.0</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Bb's Cosy Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/bb-39-s-cosy-apartments-brasov.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=21&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=295908503_329654120_0_0_0&amp;highlighted_blocks=295908503_329654120_0_0_0&amp;matching_block_id=295908503_329654120_0_0_0&amp;sr_pri_blocks=295908503_329654120_0_0_0__2194500&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,080 lei21,945 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.3</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Warm Amber Suites Brașov</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/cosmopolit-lifestyle.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=22&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=282931413_126032420_3_0_0_677855&amp;highlighted_blocks=282931413_126032420_3_0_0_677855&amp;matching_block_id=282931413_126032420_3_0_0_677855&amp;sr_pri_blocks=282931413_126032420_3_0_0_677855_3132080&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Coresi Mall Area Studios &amp; Apartments by GLAM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/coresi-mall-area-studios-amp-apartments-by-glam.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=23&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1118248102_412223809_3_0_0&amp;highlighted_blocks=1118248102_412223809_3_0_0&amp;matching_block_id=1118248102_412223809_3_0_0&amp;sr_pri_blocks=1118248102_412223809_3_0_0__2877300&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28,773 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.6</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Old Town View &amp; Balcony Apartments MM Host</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/brasov-old-town-with-mountain-view.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=24&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1428222201_417107964_3_0_0&amp;highlighted_blocks=1428222201_417107964_3_0_0&amp;matching_block_id=1428222201_417107964_3_0_0&amp;sr_pri_blocks=1428222201_417107964_3_0_0__5187930&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,993 lei16,263 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Main Square Apartments &amp; More</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/main-square-apartments-amp-more.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=25&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=116190210_208743329_0_0_0&amp;highlighted_blocks=116190210_208743329_0_0_0&amp;matching_block_id=116190210_208743329_0_0_0&amp;sr_pri_blocks=116190210_208743329_0_0_0__1626341&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7.5</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Città Studi Suites - Top Collection</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/it/bb-too-cute-2b-str8.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAKRoarKBsACAdICJDZmMGU5Mzc2LTJjYjgtNGRiMy05NWI0LWRhYmUwZjRkYzUzYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=26&amp;hapos=26&amp;sr_order=popularity&amp;srpvid=d0bf5a9436ca15d7&amp;srepoch=1766494379&amp;all_sr_blocks=120214214_373646928_1_0_0&amp;highlighted_blocks=120214214_373646928_1_0_0&amp;matching_block_id=120214214_373646928_1_0_0&amp;sr_pri_blocks=120214214_373646928_1_0_0__43850&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8.9</x:t>
-  </x:si>
-  <x:si>
-    <x:t>2,231 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Brasov Gondola Apartments</x:t>
-  </x:si>
-  <x:si>
-    <x:t>https://www.booking.com/hotel/ro/mgi-studio-coresi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuAK0qKrKBsACAdICJDA3Yjg3ODMzLWFlNmYtNDVmMi04NDkwLWQyOWNlZDU1NTgyYtgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-05-15&amp;checkout=2026-07-20&amp;dest_id=-1153613&amp;dest_type=city&amp;group_adults=3&amp;req_adults=3&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=2&amp;sr_order=popularity&amp;srpvid=f0df5c6391330050&amp;srepoch=1766495350&amp;all_sr_blocks=1413131701_413051882_0_0_0&amp;highlighted_blocks=1413131701_413051882_0_0_0&amp;matching_block_id=1413131701_413051882_0_0_0&amp;sr_pri_blocks=1413131701_413051882_0_0_0__1119300&amp;from=searchresults</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30,461 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,888 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30,849 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40,519 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>23,232 lei</x:t>
-  </x:si>
-  <x:si>
-    <x:t>33,443 lei</x:t>
+    <x:t>1,395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Heart Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cervo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=82&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8401606_88437489_1_2_0&amp;highlighted_blocks=8401606_88437489_1_2_0&amp;matching_block_id=8401606_88437489_1_2_0&amp;sr_pri_blocks=8401606_88437489_1_2_0__63455&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Carducci 22 - Sant Ambrogio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-comoda-residenza-con-terrazzino-abitabile-in-zona-sant-ambrogio.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=83&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=983710002_370801600_2_0_0&amp;highlighted_blocks=983710002_370801600_2_0_0&amp;matching_block_id=983710002_370801600_2_0_0&amp;sr_pri_blocks=983710002_370801600_2_0_0__62437&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,176</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Mythos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotel-mythos.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=84&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8999117_402390208_1_0_0&amp;highlighted_blocks=8999117_402390208_1_0_0&amp;matching_block_id=8999117_402390208_1_0_0&amp;sr_pri_blocks=8999117_402390208_1_0_0__62200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,164</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Melchiorre Gioia 30 - Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-incantevole-abitazione-in-centrale.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=85&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=1067604802_411297452_2_0_0&amp;highlighted_blocks=1067604802_411297452_2_0_0&amp;matching_block_id=1067604802_411297452_2_0_0&amp;sr_pri_blocks=1067604802_411297452_2_0_0__50615&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,575</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Vittoria</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelvittoria.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=86&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8056101_372949809_0_1_0&amp;highlighted_blocks=8056101_372949809_0_1_0&amp;matching_block_id=8056101_372949809_0_1_0&amp;sr_pri_blocks=8056101_372949809_0_1_0__62800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Enterprise Hotel Design &amp; Boutique</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/enterprisemotelmilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=87&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8081102_88434947_2_2_0_347222&amp;highlighted_blocks=8081102_88434947_2_2_0_347222&amp;matching_block_id=8081102_88434947_2_2_0_347222&amp;sr_pri_blocks=8081102_88434947_2_2_0_347222_85685&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,359</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B&amp;B Hotel Milano Sant'Ambrogio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/b-amp-b-milano-sant-39-ambrogio.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=88&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=129197701_86372636_1_2_0&amp;highlighted_blocks=129197701_86372636_1_2_0&amp;matching_block_id=129197701_86372636_1_2_0&amp;sr_pri_blocks=129197701_86372636_1_2_0__67610&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Best Western Hotel City</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bestwesternhotelcitymilano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=89&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8126205_88919885_1_2_0&amp;highlighted_blocks=8126205_88919885_1_2_0&amp;matching_block_id=8126205_88919885_1_2_0&amp;sr_pri_blocks=8126205_88919885_1_2_0__64700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,291</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lh HOTELS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/lh-hotels-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=90&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=1417299405_413407004_0_1_0&amp;highlighted_blocks=1417299405_413407004_0_1_0&amp;matching_block_id=1417299405_413407004_0_1_0&amp;sr_pri_blocks=1417299405_413407004_0_1_0__49550&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,521</x:t>
+  </x:si>
+  <x:si>
+    <x:t>iH Hotels Milano Gioia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ih-hotel-milano-gioia.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=91&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8367012_88437164_0_1_0&amp;highlighted_blocks=8367012_88437164_0_1_0&amp;matching_block_id=8367012_88437164_0_1_0&amp;sr_pri_blocks=8367012_88437164_0_1_0__44490&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,263</x:t>
+  </x:si>
+  <x:si>
+    <x:t>STAR RIBBON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/star-ribbon.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=92&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=794654905_339549249_2_2_0&amp;highlighted_blocks=794654905_339549249_2_2_0&amp;matching_block_id=794654905_339549249_2_2_0&amp;sr_pri_blocks=794654905_339549249_2_2_0__47469&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,415</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Crowne Plaza Milan City by IHG</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milan-city.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=93&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8988323_94303873_1_42_0&amp;highlighted_blocks=8988323_94303873_1_42_0&amp;matching_block_id=8988323_94303873_1_42_0&amp;sr_pri_blocks=8988323_94303873_1_42_0__88000&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,477</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residenza Cenisio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residenza-cenisio.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=94&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=28567110_88453047_0_0_0&amp;highlighted_blocks=28567110_88453047_0_0_0&amp;matching_block_id=28567110_88453047_0_0_0&amp;sr_pri_blocks=28567110_88453047_0_0_0__40250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Magenta 83D - Magenta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-monolocale-in-corso-magenta.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=95&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=955454602_368326497_2_0_0&amp;highlighted_blocks=955454602_368326497_2_0_0&amp;matching_block_id=955454602_368326497_2_0_0&amp;sr_pri_blocks=955454602_368326497_2_0_0__49770&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,532</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Aurelia Milano Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aurelia.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=96&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=8760301_88160158_0_0_0&amp;highlighted_blocks=8760301_88160158_0_0_0&amp;matching_block_id=8760301_88160158_0_0_0&amp;sr_pri_blocks=8760301_88160158_0_0_0__38185&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,943</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Bristol</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bristol-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=97&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896578&amp;all_sr_blocks=24795802_88154678_0_1_0&amp;highlighted_blocks=24795802_88154678_0_1_0&amp;matching_block_id=24795802_88154678_0_1_0&amp;sr_pri_blocks=24795802_88154678_0_1_0__57425&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,921</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CiaoMi - Hostel &amp; Long Stay - Milano Niguarda &amp; Bicocca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ciaomi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=98&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=909640012_362145726_0_0_0&amp;highlighted_blocks=909640012_362145726_0_0_0&amp;matching_block_id=909640012_362145726_0_0_0&amp;sr_pri_blocks=909640012_362145726_0_0_0__29385&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brand New Milano Porta Ticinese 70</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/brand-new-milano-porta-ticinese-70.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=99&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=1351224001_408190950_1_0_0&amp;highlighted_blocks=1351224001_408190950_1_0_0&amp;matching_block_id=1351224001_408190950_1_0_0&amp;sr_pri_blocks=1351224001_408190950_1_0_0__50361&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,562</x:t>
+  </x:si>
+  <x:si>
+    <x:t>iH Hotels Milano Lorenteggio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/holiday-inn-milan.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=100&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8799961_88160367_0_1_0&amp;highlighted_blocks=8799961_88160367_0_1_0&amp;matching_block_id=8799961_88160367_0_1_0&amp;sr_pri_blocks=8799961_88160367_0_1_0__64312&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,272</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CSI Group - Hotel Central Station</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cityhotel-central-station.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=101&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8531501_88054558_0_2_0&amp;highlighted_blocks=8531501_88054558_0_2_0&amp;matching_block_id=8531501_88054558_0_2_0&amp;sr_pri_blocks=8531501_88054558_0_2_0__47305&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hilton Milan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hilton-milan.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=102&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8894215_94301941_1_34_0&amp;highlighted_blocks=8894215_94301941_1_34_0&amp;matching_block_id=8894215_94301941_1_34_0&amp;sr_pri_blocks=8894215_94301941_1_34_0__85881&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,369</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Giardino Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/giardino-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=103&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=56422002_89615169_0_1_0&amp;highlighted_blocks=56422002_89615169_0_1_0&amp;matching_block_id=56422002_89615169_0_1_0&amp;sr_pri_blocks=56422002_89615169_0_1_0__38460&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,957</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Radisson Blu Hotel Milan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/radisson-blu-milan.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=104&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=24236402_97776892_1_1_0&amp;highlighted_blocks=24236402_97776892_1_1_0&amp;matching_block_id=24236402_97776892_1_1_0&amp;sr_pri_blocks=24236402_97776892_1_1_0__73470&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,738</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Cavour</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cavour.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=105&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8002204_88152872_1_2_0&amp;highlighted_blocks=8002204_88152872_1_2_0&amp;matching_block_id=8002204_88152872_1_2_0&amp;sr_pri_blocks=8002204_88152872_1_2_0__85040&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,326</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21 House of Stories Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/21-house-of-stories-navigli.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=106&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=924495501_364239983_1_1_0&amp;highlighted_blocks=924495501_364239983_1_1_0&amp;matching_block_id=924495501_364239983_1_1_0&amp;sr_pri_blocks=924495501_364239983_1_1_0__116780&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,941</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residence 2Gi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ajraghi-halldis-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=107&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=122518401_98061898_1_0_0&amp;highlighted_blocks=122518401_98061898_1_0_0&amp;matching_block_id=122518401_98061898_1_0_0&amp;sr_pri_blocks=122518401_98061898_1_0_0__65650&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,340</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Smart Hotel Central</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/idea-milano-centrale.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=108&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=26206501_88923901_1_2_0&amp;highlighted_blocks=26206501_88923901_1_2_0&amp;matching_block_id=26206501_88923901_1_2_0&amp;sr_pri_blocks=26206501_88923901_1_2_0__63455&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Scarlatti Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cristallo-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=109&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8492329_88920526_1_2_0&amp;highlighted_blocks=8492329_88920526_1_2_0&amp;matching_block_id=8492329_88920526_1_2_0&amp;sr_pri_blocks=8492329_88920526_1_2_0__63455&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNA Hotels Scandinavia Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/una-scandinavia.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=110&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8311403_93707953_1_2_0_779529&amp;highlighted_blocks=8311403_93707953_1_2_0_779529&amp;matching_block_id=8311403_93707953_1_2_0_779529&amp;sr_pri_blocks=8311403_93707953_1_2_0_779529_61950&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,152</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milano Ostello</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-ostello.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=111&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=274901002_106565184_0_0_0&amp;highlighted_blocks=274901002_106565184_0_0_0&amp;matching_block_id=274901002_106565184_0_0_0&amp;sr_pri_blocks=274901002_106565184_0_0_0__17430&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Dogana 3 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-raffinato-appartamento-in-duomo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=112&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=1271910702_399964166_2_0_0&amp;highlighted_blocks=1271910702_399964166_2_0_0&amp;matching_block_id=1271910702_399964166_2_0_0&amp;sr_pri_blocks=1271910702_399964166_2_0_0__70316&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,577</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Bolzano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bolzano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=113&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8759912_226124166_1_0_0&amp;highlighted_blocks=8759912_226124166_1_0_0&amp;matching_block_id=8759912_226124166_1_0_0&amp;sr_pri_blocks=8759912_226124166_1_0_0__48250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,455</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Montenapoleone Suites</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/montenapoleone-suite.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=114&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=90474505_91941993_0_0_0_434264&amp;highlighted_blocks=90474505_91941993_0_0_0_434264&amp;matching_block_id=90474505_91941993_0_0_0_434264&amp;sr_pri_blocks=90474505_91941993_0_0_0_434264_90034&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,580</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Mediolanum</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/mediolanum.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=115&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8052301_91462349_0_2_0&amp;highlighted_blocks=8052301_91462349_0_2_0&amp;matching_block_id=8052301_91462349_0_2_0&amp;sr_pri_blocks=8052301_91462349_0_2_0__55200&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,808</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Best Western Hotel Major</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/best-western-major.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=116&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8568624_88920755_1_2_0&amp;highlighted_blocks=8568624_88920755_1_2_0&amp;matching_block_id=8568624_88920755_1_2_0&amp;sr_pri_blocks=8568624_88920755_1_2_0__49250&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,505</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Canova Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/canovahotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=117&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8022107_167616899_1_2_0&amp;highlighted_blocks=8022107_167616899_1_2_0&amp;matching_block_id=8022107_167616899_1_2_0&amp;sr_pri_blocks=8022107_167616899_1_2_0__54955&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,796</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Starhotels Echo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/starhotels-echo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=118&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=21817503_91467164_1_2_0&amp;highlighted_blocks=21817503_91467164_1_2_0&amp;matching_block_id=21817503_91467164_1_2_0&amp;sr_pri_blocks=21817503_91467164_1_2_0__75000&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,815</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Starhotels Business Palace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/businesspalace.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=119&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=21817206_91467161_0_2_0&amp;highlighted_blocks=21817206_91467161_0_2_0&amp;matching_block_id=21817206_91467161_0_2_0&amp;sr_pri_blocks=21817206_91467161_0_2_0__47800&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,432</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B&amp;B HOTEL Milano Portello</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/bandb-hotel-milano-portello.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=120&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=8499810_93708116_1_2_0&amp;highlighted_blocks=8499810_93708116_1_2_0&amp;matching_block_id=8499810_93708116_1_2_0&amp;sr_pri_blocks=8499810_93708116_1_2_0__61817&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,145</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Lounge Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/urban-lounge-apartments-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=121&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=1398661303_411733212_1_0_0&amp;highlighted_blocks=1398661303_411733212_1_0_0&amp;matching_block_id=1398661303_411733212_1_0_0&amp;sr_pri_blocks=1398661303_411733212_1_0_0__58983&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milano Apartments Lombardini 1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milano-apartments-lombardini-1.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=122&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896588&amp;all_sr_blocks=1222632502_423019779_1_0_0&amp;highlighted_blocks=1222632502_423019779_1_0_0&amp;matching_block_id=1222632502_423019779_1_0_0&amp;sr_pri_blocks=1222632502_423019779_1_0_0__79750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,057</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B&amp;B Hotel Milano Central Station</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/b-amp-b-milano-central-station.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=123&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=272901306_106332019_1_2_0&amp;highlighted_blocks=272901306_106332019_1_2_0&amp;matching_block_id=272901306_106332019_1_2_0&amp;sr_pri_blocks=272901306_106332019_1_2_0__56725&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,886</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Avani Palazzo Moscova Milan Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/avani-palazzo-moscova.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=124&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=17562608_94110494_0_2_0&amp;highlighted_blocks=17562608_94110494_0_2_0&amp;matching_block_id=17562608_94110494_0_2_0&amp;sr_pri_blocks=17562608_94110494_0_2_0__82450&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Piranesi 246</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/piranesi-246.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=125&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=340652502_384712436_2_0_0&amp;highlighted_blocks=340652502_384712436_2_0_0&amp;matching_block_id=340652502_384712436_2_0_0&amp;sr_pri_blocks=340652502_384712436_2_0_0__88750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,515</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Milan Royal Suites - Centro Cadorna</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/milan-royal-suites-magenta-palace.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=126&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=86366116_88472507_2_0_0&amp;highlighted_blocks=86366116_88472507_2_0_0&amp;matching_block_id=86366116_88472507_2_0_0&amp;sr_pri_blocks=86366116_88472507_2_0_0__80926&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,117</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Marconi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelmarconi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=127&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=8042209_88153481_0_1_0&amp;highlighted_blocks=8042209_88153481_0_1_0&amp;matching_block_id=8042209_88153481_0_1_0&amp;sr_pri_blocks=8042209_88153481_0_1_0__67550&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,436</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Moscati 9A - Sarpi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-moderno-apt-con-terrazzo-in-paolo-sarpi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=128&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=984198602_411297670_2_0_0&amp;highlighted_blocks=984198602_411297670_2_0_0&amp;matching_block_id=984198602_411297670_2_0_0&amp;sr_pri_blocks=984198602_411297670_2_0_0__51397&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,615</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RELSTAY - Amendola</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/relstay-amendola.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=129&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=916337204_363124255_0_0_0&amp;highlighted_blocks=916337204_363124255_0_0_0&amp;matching_block_id=916337204_363124255_0_0_0&amp;sr_pri_blocks=916337204_363124255_0_0_0__71520&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,638</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CX Milan Bicocca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cx-milan-bicocca.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=130&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=1267984006_399515773_1_2_0&amp;highlighted_blocks=1267984006_399515773_1_2_0&amp;matching_block_id=1267984006_399515773_1_2_0&amp;sr_pri_blocks=1267984006_399515773_1_2_0__50365&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agave in Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/agave-in-centrale.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=131&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=1358611104_408185144_1_2_0&amp;highlighted_blocks=1358611104_408185144_1_2_0&amp;matching_block_id=1358611104_408185144_1_2_0&amp;sr_pri_blocks=1358611104_408185144_1_2_0__107290&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,458</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Parma</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotel-parma.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=132&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=119695206_309800589_1_1_0&amp;highlighted_blocks=119695206_309800589_1_1_0&amp;matching_block_id=119695206_309800589_1_1_0&amp;sr_pri_blocks=119695206_309800589_1_1_0__49240&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CX Milan NoM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cx-milan-nom.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=133&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=1295806401_402492832_1_1_0&amp;highlighted_blocks=1295806401_402492832_1_1_0&amp;matching_block_id=1295806401_402492832_1_1_0&amp;sr_pri_blocks=1295806401_402492832_1_1_0__40542&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,062</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Andreola Central Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/andreolacentralhotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=134&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=8078763_88153824_1_33_0&amp;highlighted_blocks=8078763_88153824_1_33_0&amp;matching_block_id=8078763_88153824_1_33_0&amp;sr_pri_blocks=8078763_88153824_1_33_0__63500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,230</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ostello Bello Milano Centrale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/ostello-bello-grande.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=135&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=8763309_90168332_0_2_0_1139570&amp;highlighted_blocks=8763309_90168332_0_2_0_1139570&amp;matching_block_id=8763309_90168332_0_2_0_1139570&amp;sr_pri_blocks=8763309_90168332_0_2_0_1139570_24941&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,269</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EasyTopStay - Moscova Modern Apartment</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/moscova-modern-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=136&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=905968401_361678059_2_0_0_852695&amp;highlighted_blocks=905968401_361678059_2_0_0_852695&amp;matching_block_id=905968401_361678059_2_0_0_852695&amp;sr_pri_blocks=905968401_361678059_2_0_0_852695_70270&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,575</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B&amp;B Hotel Milano Cenisio Garibaldi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/b-amp-b-milano-cenisio-garibaldi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=137&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=120319802_88477846_1_2_0&amp;highlighted_blocks=120319802_88477846_1_2_0&amp;matching_block_id=120319802_88477846_1_2_0&amp;sr_pri_blocks=120319802_88477846_1_2_0__57600&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,930</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Bogart Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/maryfiera.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=138&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=8052101_258805308_2_2_0&amp;highlighted_blocks=8052101_258805308_2_2_0&amp;matching_block_id=8052101_258805308_2_2_0&amp;sr_pri_blocks=8052101_258805308_2_2_0__59500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,027</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Collection Moscova Suites 8 - Top Collection</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/via-volta-apartment-moscova.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=139&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=643475901_403644755_2_0_0&amp;highlighted_blocks=643475901_403644755_2_0_0&amp;matching_block_id=643475901_403644755_2_0_0&amp;sr_pri_blocks=643475901_403644755_2_0_0__72370&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,682</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Friuli 15 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/stupendo-e-accogliente-apt-15-min-dal-duomo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=140&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=609060802_277504331_2_0_0&amp;highlighted_blocks=609060802_277504331_2_0_0&amp;matching_block_id=609060802_277504331_2_0_0&amp;sr_pri_blocks=609060802_277504331_2_0_0__46959&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,389</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urban Hive Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/carlyle.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=141&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=8035405_88919648_0_2_0&amp;highlighted_blocks=8035405_88919648_0_2_0&amp;matching_block_id=8035405_88919648_0_2_0&amp;sr_pri_blocks=8035405_88919648_0_2_0__108700&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,530</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel di Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/portaromana.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=142&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=27148817_88164853_0_1_0&amp;highlighted_blocks=27148817_88164853_0_1_0&amp;matching_block_id=27148817_88164853_0_1_0&amp;sr_pri_blocks=27148817_88164853_0_1_0__43439&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,210</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aparto Milan Giovenale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/modern-rooms-and-studios-milan-sk.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=143&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=877162712_371106738_0_0_0&amp;highlighted_blocks=877162712_371106738_0_0_0&amp;matching_block_id=877162712_371106738_0_0_0&amp;sr_pri_blocks=877162712_371106738_0_0_0__49500&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,518</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Windsor Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/windsor.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=144&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=8010816_91906915_1_1_0&amp;highlighted_blocks=8010816_91906915_1_1_0&amp;matching_block_id=8010816_91906915_1_1_0&amp;sr_pri_blocks=8010816_91906915_1_1_0__87280&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,440</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel La Vignetta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/la-vignetta.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=145&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=18750301_88162249_0_0_0&amp;highlighted_blocks=18750301_88162249_0_0_0&amp;matching_block_id=18750301_88162249_0_0_0&amp;sr_pri_blocks=18750301_88162249_0_0_0__45000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,289</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Modrone 28 S1 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/cityscape-milan-design-apartment.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=146&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=1122526001_385012587_1_0_0&amp;highlighted_blocks=1122526001_385012587_1_0_0&amp;matching_block_id=1122526001_385012587_1_0_0&amp;sr_pri_blocks=1122526001_385012587_1_0_0__57277&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,914</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Collini Rooms, WorldHotels Crafted</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/m89.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=147&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896599&amp;all_sr_blocks=223393410_98590175_1_34_0&amp;highlighted_blocks=223393410_98590175_1_34_0&amp;matching_block_id=223393410_98590175_1_34_0&amp;sr_pri_blocks=223393410_98590175_1_34_0__81000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JR Hotels Bocconi Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/top-liberty.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=148&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=8335203_88157476_1_1_0_1228740&amp;highlighted_blocks=8335203_88157476_1_1_0_1228740&amp;matching_block_id=8335203_88157476_1_1_0_1228740&amp;sr_pri_blocks=8335203_88157476_1_1_0_1228740_72031&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>iH Hotels Milano ApartHotel Argonne Park</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/biancacroce.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=149&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=23691705_88162793_0_0_0&amp;highlighted_blocks=23691705_88162793_0_0_0&amp;matching_block_id=23691705_88162793_0_0_0&amp;sr_pri_blocks=23691705_88162793_0_0_0__33752&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,717</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Joy 124 Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/joy-124-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=150&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=1235831501_395519391_1_2_0&amp;highlighted_blocks=1235831501_395519391_1_2_0&amp;matching_block_id=1235831501_395519391_1_2_0&amp;sr_pri_blocks=1235831501_395519391_1_2_0__54455&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,770</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Albani 20 - City Life</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-modern-and-spacious-apt-in-fiera-city-life.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=151&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=753188602_342458560_2_0_0&amp;highlighted_blocks=753188602_342458560_2_0_0&amp;matching_block_id=753188602_342458560_2_0_0&amp;sr_pri_blocks=753188602_342458560_2_0_0__69164&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,519</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Crema 23 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/modern-and-central-apt-in-porta-romana.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=152&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=395164201_122892247_2_0_0&amp;highlighted_blocks=395164201_122892247_2_0_0&amp;matching_block_id=395164201_122892247_2_0_0&amp;sr_pri_blocks=395164201_122892247_2_0_0__46266&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,354</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Loreto Prestige - Parking Free &amp; Bulb Gym</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/loreto-prestige.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=153&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=1239873204_395916420_3_0_0&amp;highlighted_blocks=1239873204_395916420_3_0_0&amp;matching_block_id=1239873204_395916420_3_0_0&amp;sr_pri_blocks=1239873204_395916420_3_0_0__48750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,480</x:t>
+  </x:si>
+  <x:si>
+    <x:t>B&amp;B Hotel Milano Aosta</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aosta-gruppo-mini.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=154&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=8977801_93708705_1_2_0&amp;highlighted_blocks=8977801_93708705_1_2_0&amp;matching_block_id=8977801_93708705_1_2_0&amp;sr_pri_blocks=8977801_93708705_1_2_0__67390&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,428</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hbhall Residenze Darsena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/blu-apartment-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=155&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=101681804_88400138_2_0_0&amp;highlighted_blocks=101681804_88400138_2_0_0&amp;matching_block_id=101681804_88400138_2_0_0&amp;sr_pri_blocks=101681804_88400138_2_0_0__46699&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Residenza delle Città</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/residenza-delle-citta.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=156&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=4270803_381695069_2_0_0&amp;highlighted_blocks=4270803_381695069_2_0_0&amp;matching_block_id=4270803_381695069_2_0_0&amp;sr_pri_blocks=4270803_381695069_2_0_0__68301&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,475</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Bagliori</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelbagliorimilan.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=157&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=8166101_88435896_0_2_0&amp;highlighted_blocks=8166101_88435896_0_2_0&amp;matching_block_id=8166101_88435896_0_2_0&amp;sr_pri_blocks=8166101_88435896_0_2_0__54100&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,752</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Garibaldi 59 apartments in Brera district by Rentopolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/corso-garibaldi-modern-cozy-suite-by-rentopolis.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=158&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=1307085603_403526015_1_0_0&amp;highlighted_blocks=1307085603_403526015_1_0_0&amp;matching_block_id=1307085603_403526015_1_0_0&amp;sr_pri_blocks=1307085603_403526015_1_0_0__72652&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,696</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aparto Milan Durando</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aparto-milan-durando.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=159&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=1340109402_406423656_0_0_0&amp;highlighted_blocks=1340109402_406423656_0_0_0&amp;matching_block_id=1340109402_406423656_0_0_0&amp;sr_pri_blocks=1340109402_406423656_0_0_0__28750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,463</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AV Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/esco-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=160&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=86013002_88472434_1_2_0&amp;highlighted_blocks=86013002_88472434_1_2_0&amp;matching_block_id=86013002_88472434_1_2_0&amp;sr_pri_blocks=86013002_88472434_1_2_0__60955&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Velasca Tower Apartments</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/velasca-tower-apartments-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=161&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=1275181361_400377746_1_0_0&amp;highlighted_blocks=1275181361_400377746_1_0_0&amp;matching_block_id=1275181361_400377746_1_0_0&amp;sr_pri_blocks=1275181361_400377746_1_0_0__77730&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,954</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brera Apartments in Via della Spiga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/spiga-46-suites-by-brera-apartments.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=162&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=989858402_371633451_2_0_0&amp;highlighted_blocks=989858402_371633451_2_0_0&amp;matching_block_id=989858402_371633451_2_0_0&amp;sr_pri_blocks=989858402_371633451_2_0_0__85415&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Lecco 11P3 - Porta Venezia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/tropical-and-new-flat-in-porta-venezia-by-easylife.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=163&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=881074302_411297533_2_0_0&amp;highlighted_blocks=881074302_411297533_2_0_0&amp;matching_block_id=881074302_411297533_2_0_0&amp;sr_pri_blocks=881074302_411297533_2_0_0__56758&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Pierre Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/pierre-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=164&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=8512401_91907597_0_1_0&amp;highlighted_blocks=8512401_91907597_0_1_0&amp;matching_block_id=8512401_91907597_0_1_0&amp;sr_pri_blocks=8512401_91907597_0_1_0__98517&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MEININGER Milano Lambrate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/meininger-milano-lambrate.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=165&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=350395709_117675704_0_2_0_496119&amp;highlighted_blocks=350395709_117675704_0_2_0_496119&amp;matching_block_id=350395709_117675704_0_2_0_496119&amp;sr_pri_blocks=350395709_117675704_0_2_0_496119_21075&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,072</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Agape Hotel - AA Hotels</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/agapehotel.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=166&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=8289812_93707913_0_2_0_1292544&amp;highlighted_blocks=8289812_93707913_0_2_0_1292544&amp;matching_block_id=8289812_93707913_0_2_0_1292544&amp;sr_pri_blocks=8289812_93707913_0_2_0_1292544_44825&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,280</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Landscape Flats</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/landscape-flats.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=167&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=1250259201_397504852_1_0_0&amp;highlighted_blocks=1250259201_397504852_1_0_0&amp;matching_block_id=1250259201_397504852_1_0_0&amp;sr_pri_blocks=1250259201_397504852_1_0_0__57554&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,928</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Toiletpaper Living</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/toiletpaper-living.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=168&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=1184641403_390835896_2_0_0&amp;highlighted_blocks=1184641403_390835896_2_0_0&amp;matching_block_id=1184641403_390835896_2_0_0&amp;sr_pri_blocks=1184641403_390835896_2_0_0__79338&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,036</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Montecarlo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/montecarlo-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=169&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=27560315_88165063_0_2_0&amp;highlighted_blocks=27560315_88165063_0_2_0&amp;matching_block_id=27560315_88165063_0_2_0&amp;sr_pri_blocks=27560315_88165063_0_2_0__42700&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Ariston</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hotelariston.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=170&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=8035201_88153450_0_1_0&amp;highlighted_blocks=8035201_88153450_0_1_0&amp;matching_block_id=8035201_88153450_0_1_0&amp;sr_pri_blocks=8035201_88153450_0_1_0__85325&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,341</x:t>
+  </x:si>
+  <x:si>
+    <x:t>APARTHOTEL CASA MIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/aparthotel-casa-mia.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=171&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=481374404_361771404_0_0_0&amp;highlighted_blocks=481374404_361771404_0_0_0&amp;matching_block_id=481374404_361771404_0_0_0&amp;sr_pri_blocks=481374404_361771404_0_0_0__79750&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Pier Lombardo 16 - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nice-and-cozy-studio-in-porta-romana-by-easylife.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=172&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896610&amp;all_sr_blocks=794224002_342458649_0_0_0&amp;highlighted_blocks=794224002_342458649_0_0_0&amp;matching_block_id=794224002_342458649_0_0_0&amp;sr_pri_blocks=794224002_342458649_0_0_0__43178&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.8</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,197</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Villa Massari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/italian-residencies-villa-massari.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=1&amp;hapos=173&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=970311603_369428409_2_0_0&amp;highlighted_blocks=970311603_369428409_2_0_0&amp;matching_block_id=970311603_369428409_2_0_0&amp;sr_pri_blocks=970311603_369428409_2_0_0__51145&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,602</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Starhotels Tourist</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/starhotels-tourist.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=2&amp;hapos=174&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=18723_93715487_0_0_0&amp;highlighted_blocks=18723_93715487_0_0_0&amp;matching_block_id=18723_93715487_0_0_0&amp;sr_pri_blocks=18723_93715487_0_0_0__51000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,594</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Ferrari 9 - Navigli</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-e-moderno-bilocale-in-zona-navigli.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=3&amp;hapos=175&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=941565102_411297408_2_0_0&amp;highlighted_blocks=941565102_411297408_2_0_0&amp;matching_block_id=941565102_411297408_2_0_0&amp;sr_pri_blocks=941565102_411297408_2_0_0__53318&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GREEN RIBBON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/green-ribbon.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=4&amp;hapos=176&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=643672405_263835080_2_2_0&amp;highlighted_blocks=643672405_263835080_2_2_0&amp;matching_block_id=643672405_263835080_2_2_0&amp;sr_pri_blocks=643672405_263835080_2_2_0__52405&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,666</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grand Visconti Palace</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/grand-visconti-palace.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=5&amp;hapos=177&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8335451_91907352_0_2_0&amp;highlighted_blocks=8335451_91907352_0_2_0&amp;matching_block_id=8335451_91907352_0_2_0&amp;sr_pri_blocks=8335451_91907352_0_2_0__100427&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Maffucci 53 - Dergano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-accogliente-dimora-con-balcone.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=6&amp;hapos=178&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=987239102_411297538_2_0_0&amp;highlighted_blocks=987239102_411297538_2_0_0&amp;matching_block_id=987239102_411297538_2_0_0&amp;sr_pri_blocks=987239102_411297538_2_0_0__48141&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,449</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Lovelyloft - Alzaia Naviglio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/lovelyloft-alzaia-naviglio.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=7&amp;hapos=179&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=211441401_96023455_2_0_0&amp;highlighted_blocks=211441401_96023455_2_0_0&amp;matching_block_id=211441401_96023455_2_0_0&amp;sr_pri_blocks=211441401_96023455_2_0_0__39801&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,025</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HD8 Hotel Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/hd8-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=8&amp;hapos=180&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=541256202_193697885_0_2_0&amp;highlighted_blocks=541256202_193697885_0_2_0&amp;matching_block_id=541256202_193697885_0_2_0&amp;sr_pri_blocks=541256202_193697885_0_2_0__63455&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WHITE RIBBON</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/white-ribbon.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=9&amp;hapos=181&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=643673707_263834474_2_2_0&amp;highlighted_blocks=643673707_263834474_2_2_0&amp;matching_block_id=643673707_263834474_2_2_0&amp;sr_pri_blocks=643673707_263834474_2_2_0__46644&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,373</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IL RICCIO Rooms</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/appartamento-5-8.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=10&amp;hapos=182&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=194131811_193349804_1_0_0&amp;highlighted_blocks=194131811_193349804_1_0_0&amp;matching_block_id=194131811_193349804_1_0_0&amp;sr_pri_blocks=194131811_193349804_1_0_0__58943&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,999</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CASATI CENTRAL STATION Metro M1, M2, M3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/casati-central-station-metro-m1-m2-m3.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=11&amp;hapos=183&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=1366308501_408912923_2_0_0&amp;highlighted_blocks=1366308501_408912923_2_0_0&amp;matching_block_id=1366308501_408912923_2_0_0&amp;sr_pri_blocks=1366308501_408912923_2_0_0__73056&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,717</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - MonteNero 29 D - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/beautiful-studio-at-10-mins-from-duomo-by-easylife.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=12&amp;hapos=184&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=819226901_344556970_0_0_0&amp;highlighted_blocks=819226901_344556970_0_0_0&amp;matching_block_id=819226901_344556970_0_0_0&amp;sr_pri_blocks=819226901_344556970_0_0_0__39590&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,014</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nhow Milan</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nhow-milano.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=13&amp;hapos=185&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8478903_94109628_0_2_0&amp;highlighted_blocks=8478903_94109628_0_2_0&amp;matching_block_id=8478903_94109628_0_2_0&amp;sr_pri_blocks=8478903_94109628_0_2_0__94000&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,782</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH Collection Milano Touring</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nh-collection-milano-touring.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=14&amp;hapos=186&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8172464_94109425_0_2_0&amp;highlighted_blocks=8172464_94109425_0_2_0&amp;matching_block_id=8172464_94109425_0_2_0&amp;sr_pri_blocks=8172464_94109425_0_2_0__91100&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,634</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tivoli President Milano Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nh-collection-milano-president.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=15&amp;hapos=187&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=22609427_94353447_0_34_0&amp;highlighted_blocks=22609427_94353447_0_34_0&amp;matching_block_id=22609427_94353447_0_34_0&amp;sr_pri_blocks=22609427_94353447_0_34_0__190750&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,704</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Best Western Plus The Hub Hotel</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/the-hub.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=16&amp;hapos=188&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=23572055_88443312_1_2_0&amp;highlighted_blocks=23572055_88443312_1_2_0&amp;matching_block_id=23572055_88443312_1_2_0&amp;sr_pri_blocks=23572055_88443312_1_2_0__44000&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,238</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Washington 91 p7 - Solari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-elegante-appartamento-in-solari.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=17&amp;hapos=189&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=1085204302_381393382_2_0_0&amp;highlighted_blocks=1085204302_381393382_2_0_0&amp;matching_block_id=1085204302_381393382_2_0_0&amp;sr_pri_blocks=1085204302_381393382_2_0_0__54814&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,789</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Crocetta 2 P1S - Porta Romana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easylife-moderno-bilocale-in-zona-porta-romana.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=18&amp;hapos=190&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=913089902_411297669_2_0_0&amp;highlighted_blocks=913089902_411297669_2_0_0&amp;matching_block_id=913089902_411297669_2_0_0&amp;sr_pri_blocks=913089902_411297669_2_0_0__54018&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,748</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH Collection Porta Nuova</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/nh-milano-grand-hotel-verdi.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=19&amp;hapos=191&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8019943_94109154_0_2_0&amp;highlighted_blocks=8019943_94109154_0_2_0&amp;matching_block_id=8019943_94109154_0_2_0&amp;sr_pri_blocks=8019943_94109154_0_2_0__95650&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,866</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Leonardo Hotel Milan City Center</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/leonardo-hotels-milan.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=20&amp;hapos=192&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8008117_91462307_0_2_0&amp;highlighted_blocks=8008117_91462307_0_2_0&amp;matching_block_id=8008117_91462307_0_2_0&amp;sr_pri_blocks=8008117_91462307_0_2_0__79790&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,059</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNA Hotels Century Milano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/centurytower.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=21&amp;hapos=193&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8001402_91462284_2_2_0_779414&amp;highlighted_blocks=8001402_91462284_2_2_0_779414&amp;matching_block_id=8001402_91462284_2_2_0_779414&amp;sr_pri_blocks=8001402_91462284_2_2_0_779414_100000&amp;from_sustainable_property_sr=1&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,087</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Sina De La Ville</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/sina-de-la-ville.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=22&amp;hapos=194&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=8328902_91462447_1_33_0&amp;highlighted_blocks=8328902_91462447_1_33_0&amp;matching_block_id=8328902_91462447_1_33_0&amp;sr_pri_blocks=8328902_91462447_1_33_0__153900&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,829</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easystudio Milan - Solari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/easystudio-milan-solari.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=23&amp;hapos=195&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=1057394804_377969332_0_0_0&amp;highlighted_blocks=1057394804_377969332_0_0_0&amp;matching_block_id=1057394804_377969332_0_0_0&amp;sr_pri_blocks=1057394804_377969332_0_0_0__34523&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1,756</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Hotel Midway</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/midway.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=24&amp;hapos=196&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=899561101_360651900_0_2_0&amp;highlighted_blocks=899561101_360651900_0_2_0&amp;matching_block_id=899561101_360651900_0_2_0&amp;sr_pri_blocks=899561101_360651900_0_2_0__54850&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2,790</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Easylife - Milano - Correnti 24 - Duomo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>https://www.booking.com/hotel/it/elegante-e-completamente-arredato-apt-in-duomo.html?label=gen173nr-10CAEoggI46AdIM1gEaMABiAEBmAEzuAEXyAEM2AED6AEB-AEBiAIBqAIBuALo6__KBsACAdICJDJlMzcyZTBjLTdkZmEtNGYyZS04YTFjLWIzZGUwYmJmOGVlONgCAeACAQ&amp;aid=304142&amp;ucfs=1&amp;arphpl=1&amp;checkin=2026-08-10&amp;checkout=2026-08-15&amp;dest_id=-121726&amp;dest_type=city&amp;group_adults=1&amp;req_adults=1&amp;no_rooms=1&amp;group_children=0&amp;req_children=0&amp;hpos=25&amp;hapos=197&amp;sr_order=popularity&amp;srpvid=48553e017da403376dac50b06576c0ea&amp;srepoch=1767896621&amp;all_sr_blocks=414851001_126389632_2_0_0&amp;highlighted_blocks=414851001_126389632_2_0_0&amp;matching_block_id=414851001_126389632_2_0_0&amp;sr_pri_blocks=414851001_126389632_2_0_0__64837&amp;from=searchresults</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,298</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -658,7 +2200,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:C26"/>
+  <x:dimension ref="A1:D26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
     <x:row r="1" spans="1:4">
@@ -677,366 +2219,2760 @@
     </x:row>
     <x:row r="2" spans="1:4">
       <x:c r="A2" s="0" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="3" spans="1:4">
       <x:c r="A3" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B3" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
-      <x:c r="B3" s="0" t="s">
-        <x:v>91</x:v>
-      </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>11</x:v>
       </x:c>
     </x:row>
     <x:row r="4" spans="1:4">
       <x:c r="A4" s="0" t="s">
+        <x:v>12</x:v>
+      </x:c>
+      <x:c r="B4" s="0" t="s">
         <x:v>9</x:v>
       </x:c>
-      <x:c r="B4" s="0" t="s">
-        <x:v>10</x:v>
-      </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>15</x:v>
       </x:c>
     </x:row>
     <x:row r="5" spans="1:4">
       <x:c r="A5" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="B5" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B5" s="0" t="s">
-        <x:v>14</x:v>
-      </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>19</x:v>
       </x:c>
     </x:row>
     <x:row r="6" spans="1:4">
       <x:c r="A6" s="0" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B6" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
-      <x:c r="B6" s="0" t="s">
-        <x:v>18</x:v>
-      </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>94</x:v>
+        <x:v>22</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:4">
       <x:c r="A7" s="0" t="s">
-        <x:v>20</x:v>
+        <x:v>23</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
         <x:v>21</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>22</x:v>
+        <x:v>7</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:4">
       <x:c r="A8" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="B8" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
-      <x:c r="B8" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>28</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:4">
       <x:c r="A9" s="0" t="s">
-        <x:v>28</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>23</x:v>
+        <x:v>31</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:4">
       <x:c r="A10" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>35</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:4">
       <x:c r="A11" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>39</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:4">
       <x:c r="A12" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>43</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:4">
       <x:c r="A13" s="0" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="B13" s="0" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="B13" s="0" t="s">
-        <x:v>42</x:v>
-      </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>46</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:4">
       <x:c r="A14" s="0" t="s">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="B14" s="0" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="B14" s="0" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>50</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:4">
       <x:c r="A15" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>50</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:4">
       <x:c r="A16" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B16" s="0" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B16" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>57</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:4">
       <x:c r="A17" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B17" s="0" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B17" s="0" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>34</x:v>
+        <x:v>61</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:4">
       <x:c r="A18" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>16</x:v>
+        <x:v>63</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:4">
       <x:c r="A19" s="0" t="s">
-        <x:v>61</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:4">
       <x:c r="A20" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>15</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>71</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:4">
       <x:c r="A21" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:4">
       <x:c r="A22" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>77</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:4">
       <x:c r="A23" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>80</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:4">
       <x:c r="A24" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>84</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:4">
       <x:c r="A25" s="0" t="s">
-        <x:v>80</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>19</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>83</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:4">
       <x:c r="A26" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>90</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:4">
       <x:c r="A27" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="C27" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D27" s="0" t="s">
+        <x:v>94</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:4">
+      <x:c r="A28" s="0" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="B28" s="0" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="C28" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D28" s="0" t="s">
+        <x:v>97</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:4">
+      <x:c r="A29" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="B29" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="C29" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D29" s="0" t="s">
+        <x:v>100</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:4">
+      <x:c r="A30" s="0" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="B30" s="0" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="C30" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D30" s="0" t="s">
+        <x:v>104</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:4">
+      <x:c r="A31" s="0" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="B31" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="C31" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D31" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:4">
+      <x:c r="A32" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="B32" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="C32" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D32" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:4">
+      <x:c r="A33" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="B33" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="C33" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D33" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:4">
+      <x:c r="A34" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B34" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C34" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D34" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:4">
+      <x:c r="A35" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="B35" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="C35" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D35" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:4">
+      <x:c r="A36" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="B36" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="C36" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D36" s="0" t="s">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:4">
+      <x:c r="A37" s="0" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="B37" s="0" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="C37" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D37" s="0" t="s">
+        <x:v>128</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:4">
+      <x:c r="A38" s="0" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="B38" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="C38" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D38" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:4">
+      <x:c r="A39" s="0" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="B39" s="0" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="C39" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D39" s="0" t="s">
+        <x:v>134</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:4">
+      <x:c r="A40" s="0" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="B40" s="0" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="C40" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D40" s="0" t="s">
+        <x:v>137</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:4">
+      <x:c r="A41" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="B41" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="C41" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D41" s="0" t="s">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:4">
+      <x:c r="A42" s="0" t="s">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="B42" s="0" t="s">
+        <x:v>142</x:v>
+      </x:c>
+      <x:c r="C42" s="0" t="s">
+        <x:v>143</x:v>
+      </x:c>
+      <x:c r="D42" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:4">
+      <x:c r="A43" s="0" t="s">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="B43" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="C43" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D43" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:4">
+      <x:c r="A44" s="0" t="s">
+        <x:v>148</x:v>
+      </x:c>
+      <x:c r="B44" s="0" t="s">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="C44" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D44" s="0" t="s">
+        <x:v>150</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:4">
+      <x:c r="A45" s="0" t="s">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="B45" s="0" t="s">
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="C45" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D45" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:4">
+      <x:c r="A46" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="B46" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="C46" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D46" s="0" t="s">
+        <x:v>156</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:4">
+      <x:c r="A47" s="0" t="s">
+        <x:v>157</x:v>
+      </x:c>
+      <x:c r="B47" s="0" t="s">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="C47" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D47" s="0" t="s">
+        <x:v>159</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:4">
+      <x:c r="A48" s="0" t="s">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="B48" s="0" t="s">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="C48" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D48" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:4">
+      <x:c r="A49" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+      <x:c r="B49" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="C49" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D49" s="0" t="s">
+        <x:v>165</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:4">
+      <x:c r="A50" s="0" t="s">
+        <x:v>166</x:v>
+      </x:c>
+      <x:c r="B50" s="0" t="s">
+        <x:v>167</x:v>
+      </x:c>
+      <x:c r="C50" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D50" s="0" t="s">
+        <x:v>168</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:4">
+      <x:c r="A51" s="0" t="s">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="B51" s="0" t="s">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="C51" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D51" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:4">
+      <x:c r="A52" s="0" t="s">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="B52" s="0" t="s">
+        <x:v>174</x:v>
+      </x:c>
+      <x:c r="C52" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D52" s="0" t="s">
+        <x:v>175</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:4">
+      <x:c r="A53" s="0" t="s">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="B53" s="0" t="s">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="C53" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D53" s="0" t="s">
+        <x:v>178</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:4">
+      <x:c r="A54" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="B54" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="C54" s="0" t="s">
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="D54" s="0" t="s">
+        <x:v>182</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:4">
+      <x:c r="A55" s="0" t="s">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="B55" s="0" t="s">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="C55" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D55" s="0" t="s">
+        <x:v>186</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:4">
+      <x:c r="A56" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="B56" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="C56" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D56" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:4">
+      <x:c r="A57" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="B57" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="C57" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D57" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:4">
+      <x:c r="A58" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="B58" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="C58" s="0" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="C27" s="0" t="s">
-        <x:v>88</x:v>
-      </x:c>
-      <x:c r="D27" s="0" t="s">
-        <x:v>89</x:v>
+      <x:c r="D58" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:4">
+      <x:c r="A59" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>198</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:4">
+      <x:c r="A60" s="0" t="s">
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>202</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:4">
+      <x:c r="A61" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>205</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:4">
+      <x:c r="A62" s="0" t="s">
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>208</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:4">
+      <x:c r="A63" s="0" t="s">
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:4">
+      <x:c r="A64" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:4">
+      <x:c r="A65" s="0" t="s">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:4">
+      <x:c r="A66" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>222</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:4">
+      <x:c r="A67" s="0" t="s">
+        <x:v>223</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>225</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:4">
+      <x:c r="A68" s="0" t="s">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>229</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:4">
+      <x:c r="A69" s="0" t="s">
+        <x:v>230</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>231</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>232</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:4">
+      <x:c r="A70" s="0" t="s">
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:4">
+      <x:c r="A71" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>153</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:4">
+      <x:c r="A72" s="0" t="s">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>239</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>240</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:4">
+      <x:c r="A73" s="0" t="s">
+        <x:v>241</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:4">
+      <x:c r="A74" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>246</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:4">
+      <x:c r="A75" s="0" t="s">
+        <x:v>247</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>249</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:4">
+      <x:c r="A76" s="0" t="s">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:4">
+      <x:c r="A77" s="0" t="s">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>256</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:4">
+      <x:c r="A78" s="0" t="s">
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:4">
+      <x:c r="A79" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>261</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>262</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:4">
+      <x:c r="A80" s="0" t="s">
+        <x:v>263</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>264</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>266</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:4">
+      <x:c r="A81" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:4">
+      <x:c r="A82" s="0" t="s">
+        <x:v>270</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>271</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>273</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:4">
+      <x:c r="A83" s="0" t="s">
+        <x:v>274</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:4">
+      <x:c r="A84" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:4">
+      <x:c r="A85" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:4">
+      <x:c r="A86" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:4">
+      <x:c r="A87" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>286</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>287</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:4">
+      <x:c r="A88" s="0" t="s">
+        <x:v>288</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>289</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>290</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:4">
+      <x:c r="A89" s="0" t="s">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:4">
+      <x:c r="A90" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>294</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>295</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:4">
+      <x:c r="A91" s="0" t="s">
+        <x:v>296</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>297</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>298</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:4">
+      <x:c r="A92" s="0" t="s">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:4">
+      <x:c r="A93" s="0" t="s">
+        <x:v>302</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>304</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:4">
+      <x:c r="A94" s="0" t="s">
+        <x:v>305</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>306</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>307</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:4">
+      <x:c r="A95" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>310</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:4">
+      <x:c r="A96" s="0" t="s">
+        <x:v>311</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>312</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>313</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:4">
+      <x:c r="A97" s="0" t="s">
+        <x:v>314</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:4">
+      <x:c r="A98" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>318</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>319</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:4">
+      <x:c r="A99" s="0" t="s">
+        <x:v>320</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>321</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>144</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:4">
+      <x:c r="A100" s="0" t="s">
+        <x:v>322</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:4">
+      <x:c r="A101" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+      <x:c r="B101" s="0" t="s">
+        <x:v>326</x:v>
+      </x:c>
+      <x:c r="C101" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D101" s="0" t="s">
+        <x:v>327</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:4">
+      <x:c r="A102" s="0" t="s">
+        <x:v>328</x:v>
+      </x:c>
+      <x:c r="B102" s="0" t="s">
+        <x:v>329</x:v>
+      </x:c>
+      <x:c r="C102" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D102" s="0" t="s">
+        <x:v>330</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:4">
+      <x:c r="A103" s="0" t="s">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="B103" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="C103" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D103" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:4">
+      <x:c r="A104" s="0" t="s">
+        <x:v>334</x:v>
+      </x:c>
+      <x:c r="B104" s="0" t="s">
+        <x:v>335</x:v>
+      </x:c>
+      <x:c r="C104" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D104" s="0" t="s">
+        <x:v>336</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:4">
+      <x:c r="A105" s="0" t="s">
+        <x:v>337</x:v>
+      </x:c>
+      <x:c r="B105" s="0" t="s">
+        <x:v>338</x:v>
+      </x:c>
+      <x:c r="C105" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D105" s="0" t="s">
+        <x:v>339</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:4">
+      <x:c r="A106" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="B106" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+      <x:c r="C106" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D106" s="0" t="s">
+        <x:v>342</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:4">
+      <x:c r="A107" s="0" t="s">
+        <x:v>343</x:v>
+      </x:c>
+      <x:c r="B107" s="0" t="s">
+        <x:v>344</x:v>
+      </x:c>
+      <x:c r="C107" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D107" s="0" t="s">
+        <x:v>345</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:4">
+      <x:c r="A108" s="0" t="s">
+        <x:v>346</x:v>
+      </x:c>
+      <x:c r="B108" s="0" t="s">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="C108" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D108" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:4">
+      <x:c r="A109" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+      <x:c r="B109" s="0" t="s">
+        <x:v>350</x:v>
+      </x:c>
+      <x:c r="C109" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D109" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:4">
+      <x:c r="A110" s="0" t="s">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="B110" s="0" t="s">
+        <x:v>352</x:v>
+      </x:c>
+      <x:c r="C110" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D110" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:4">
+      <x:c r="A111" s="0" t="s">
+        <x:v>353</x:v>
+      </x:c>
+      <x:c r="B111" s="0" t="s">
+        <x:v>354</x:v>
+      </x:c>
+      <x:c r="C111" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D111" s="0" t="s">
+        <x:v>355</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:4">
+      <x:c r="A112" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="B112" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+      <x:c r="C112" s="0" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="D112" s="0" t="s">
+        <x:v>358</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:4">
+      <x:c r="A113" s="0" t="s">
+        <x:v>359</x:v>
+      </x:c>
+      <x:c r="B113" s="0" t="s">
+        <x:v>360</x:v>
+      </x:c>
+      <x:c r="C113" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D113" s="0" t="s">
+        <x:v>361</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:4">
+      <x:c r="A114" s="0" t="s">
+        <x:v>362</x:v>
+      </x:c>
+      <x:c r="B114" s="0" t="s">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="C114" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D114" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:4">
+      <x:c r="A115" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+      <x:c r="B115" s="0" t="s">
+        <x:v>366</x:v>
+      </x:c>
+      <x:c r="C115" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D115" s="0" t="s">
+        <x:v>367</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:4">
+      <x:c r="A116" s="0" t="s">
+        <x:v>368</x:v>
+      </x:c>
+      <x:c r="B116" s="0" t="s">
+        <x:v>369</x:v>
+      </x:c>
+      <x:c r="C116" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D116" s="0" t="s">
+        <x:v>370</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:4">
+      <x:c r="A117" s="0" t="s">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="B117" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="C117" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D117" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:4">
+      <x:c r="A118" s="0" t="s">
+        <x:v>374</x:v>
+      </x:c>
+      <x:c r="B118" s="0" t="s">
+        <x:v>375</x:v>
+      </x:c>
+      <x:c r="C118" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D118" s="0" t="s">
+        <x:v>376</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:4">
+      <x:c r="A119" s="0" t="s">
+        <x:v>377</x:v>
+      </x:c>
+      <x:c r="B119" s="0" t="s">
+        <x:v>378</x:v>
+      </x:c>
+      <x:c r="C119" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D119" s="0" t="s">
+        <x:v>379</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:4">
+      <x:c r="A120" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D120" s="0" t="s">
+        <x:v>382</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:4">
+      <x:c r="A121" s="0" t="s">
+        <x:v>383</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>384</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D121" s="0" t="s">
+        <x:v>385</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="122" spans="1:4">
+      <x:c r="A122" s="0" t="s">
+        <x:v>386</x:v>
+      </x:c>
+      <x:c r="B122" s="0" t="s">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="C122" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D122" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="123" spans="1:4">
+      <x:c r="A123" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+      <x:c r="B123" s="0" t="s">
+        <x:v>390</x:v>
+      </x:c>
+      <x:c r="C123" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D123" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="124" spans="1:4">
+      <x:c r="A124" s="0" t="s">
+        <x:v>392</x:v>
+      </x:c>
+      <x:c r="B124" s="0" t="s">
+        <x:v>393</x:v>
+      </x:c>
+      <x:c r="C124" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D124" s="0" t="s">
+        <x:v>394</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="125" spans="1:4">
+      <x:c r="A125" s="0" t="s">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="B125" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="C125" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D125" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="126" spans="1:4">
+      <x:c r="A126" s="0" t="s">
+        <x:v>398</x:v>
+      </x:c>
+      <x:c r="B126" s="0" t="s">
+        <x:v>399</x:v>
+      </x:c>
+      <x:c r="C126" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D126" s="0" t="s">
+        <x:v>400</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="127" spans="1:4">
+      <x:c r="A127" s="0" t="s">
+        <x:v>401</x:v>
+      </x:c>
+      <x:c r="B127" s="0" t="s">
+        <x:v>402</x:v>
+      </x:c>
+      <x:c r="C127" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D127" s="0" t="s">
+        <x:v>403</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="128" spans="1:4">
+      <x:c r="A128" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="B128" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+      <x:c r="C128" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D128" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="129" spans="1:4">
+      <x:c r="A129" s="0" t="s">
+        <x:v>407</x:v>
+      </x:c>
+      <x:c r="B129" s="0" t="s">
+        <x:v>408</x:v>
+      </x:c>
+      <x:c r="C129" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D129" s="0" t="s">
+        <x:v>409</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="130" spans="1:4">
+      <x:c r="A130" s="0" t="s">
+        <x:v>410</x:v>
+      </x:c>
+      <x:c r="B130" s="0" t="s">
+        <x:v>411</x:v>
+      </x:c>
+      <x:c r="C130" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D130" s="0" t="s">
+        <x:v>412</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="131" spans="1:4">
+      <x:c r="A131" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="B131" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+      <x:c r="C131" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D131" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="132" spans="1:4">
+      <x:c r="A132" s="0" t="s">
+        <x:v>415</x:v>
+      </x:c>
+      <x:c r="B132" s="0" t="s">
+        <x:v>416</x:v>
+      </x:c>
+      <x:c r="C132" s="0" t="s">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="D132" s="0" t="s">
+        <x:v>417</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="133" spans="1:4">
+      <x:c r="A133" s="0" t="s">
+        <x:v>418</x:v>
+      </x:c>
+      <x:c r="B133" s="0" t="s">
+        <x:v>419</x:v>
+      </x:c>
+      <x:c r="C133" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D133" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="134" spans="1:4">
+      <x:c r="A134" s="0" t="s">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="B134" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="C134" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D134" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="135" spans="1:4">
+      <x:c r="A135" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="B135" s="0" t="s">
+        <x:v>424</x:v>
+      </x:c>
+      <x:c r="C135" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D135" s="0" t="s">
+        <x:v>425</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="136" spans="1:4">
+      <x:c r="A136" s="0" t="s">
+        <x:v>426</x:v>
+      </x:c>
+      <x:c r="B136" s="0" t="s">
+        <x:v>427</x:v>
+      </x:c>
+      <x:c r="C136" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D136" s="0" t="s">
+        <x:v>428</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="137" spans="1:4">
+      <x:c r="A137" s="0" t="s">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="B137" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="C137" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D137" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="138" spans="1:4">
+      <x:c r="A138" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="B138" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+      <x:c r="C138" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D138" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="139" spans="1:4">
+      <x:c r="A139" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="B139" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="C139" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D139" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="140" spans="1:4">
+      <x:c r="A140" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="B140" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="C140" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="D140" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="141" spans="1:4">
+      <x:c r="A141" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="B141" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="C141" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D141" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="142" spans="1:4">
+      <x:c r="A142" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B142" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="C142" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D142" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="143" spans="1:4">
+      <x:c r="A143" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="B143" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="C143" s="0" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D143" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="144" spans="1:4">
+      <x:c r="A144" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="B144" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+      <x:c r="C144" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D144" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="145" spans="1:4">
+      <x:c r="A145" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="B145" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="C145" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D145" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="146" spans="1:4">
+      <x:c r="A146" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="B146" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="C146" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D146" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="147" spans="1:4">
+      <x:c r="A147" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+      <x:c r="B147" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="C147" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D147" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="148" spans="1:4">
+      <x:c r="A148" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="B148" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="C148" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D148" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="149" spans="1:4">
+      <x:c r="A149" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="B149" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="C149" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D149" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="150" spans="1:4">
+      <x:c r="A150" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B150" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C150" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D150" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="151" spans="1:4">
+      <x:c r="A151" s="0" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="B151" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="C151" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D151" s="0" t="s">
+        <x:v>473</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="152" spans="1:4">
+      <x:c r="A152" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="B152" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+      <x:c r="C152" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D152" s="0" t="s">
+        <x:v>476</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="153" spans="1:4">
+      <x:c r="A153" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="B153" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="C153" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D153" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="154" spans="1:4">
+      <x:c r="A154" s="0" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="B154" s="0" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="C154" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D154" s="0" t="s">
+        <x:v>482</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="155" spans="1:4">
+      <x:c r="A155" s="0" t="s">
+        <x:v>483</x:v>
+      </x:c>
+      <x:c r="B155" s="0" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="C155" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D155" s="0" t="s">
+        <x:v>485</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="156" spans="1:4">
+      <x:c r="A156" s="0" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="B156" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="C156" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D156" s="0" t="s">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="157" spans="1:4">
+      <x:c r="A157" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="B157" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="C157" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D157" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="158" spans="1:4">
+      <x:c r="A158" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+      <x:c r="B158" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="C158" s="0" t="s">
+        <x:v>27</x:v>
+      </x:c>
+      <x:c r="D158" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="159" spans="1:4">
+      <x:c r="A159" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="B159" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="C159" s="0" t="s">
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="D159" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="160" spans="1:4">
+      <x:c r="A160" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="B160" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="C160" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D160" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="161" spans="1:4">
+      <x:c r="A161" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="B161" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="C161" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D161" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="162" spans="1:4">
+      <x:c r="A162" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="B162" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="C162" s="0" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="D162" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="163" spans="1:4">
+      <x:c r="A163" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="B163" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="C163" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D163" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="164" spans="1:4">
+      <x:c r="A164" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B164" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="C164" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D164" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="165" spans="1:4">
+      <x:c r="A165" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="B165" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="C165" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D165" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="166" spans="1:4">
+      <x:c r="A166" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="B166" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="C166" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D166" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="167" spans="1:4">
+      <x:c r="A167" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="B167" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="C167" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D167" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="168" spans="1:4">
+      <x:c r="A168" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="B168" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="C168" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D168" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="169" spans="1:4">
+      <x:c r="A169" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="B169" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="C169" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D169" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="170" spans="1:4">
+      <x:c r="A170" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+      <x:c r="B170" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="C170" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D170" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="171" spans="1:4">
+      <x:c r="A171" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="B171" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="C171" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D171" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="172" spans="1:4">
+      <x:c r="A172" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="B172" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="C172" s="0" t="s">
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="D172" s="0" t="s">
+        <x:v>391</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="173" spans="1:4">
+      <x:c r="A173" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+      <x:c r="B173" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="C173" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="D173" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="174" spans="1:4">
+      <x:c r="A174" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="B174" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="C174" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D174" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="175" spans="1:4">
+      <x:c r="A175" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="B175" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="C175" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D175" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="176" spans="1:4">
+      <x:c r="A176" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B176" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="C176" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D176" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="177" spans="1:4">
+      <x:c r="A177" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="B177" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="C177" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D177" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="178" spans="1:4">
+      <x:c r="A178" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="B178" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+      <x:c r="C178" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D178" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="179" spans="1:4">
+      <x:c r="A179" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="B179" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="C179" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D179" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="180" spans="1:4">
+      <x:c r="A180" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="B180" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="C180" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="D180" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="181" spans="1:4">
+      <x:c r="A181" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+      <x:c r="B181" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="C181" s="0" t="s">
+        <x:v>18</x:v>
+      </x:c>
+      <x:c r="D181" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="182" spans="1:4">
+      <x:c r="A182" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="B182" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="C182" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D182" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="183" spans="1:4">
+      <x:c r="A183" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="B183" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="C183" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D183" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="184" spans="1:4">
+      <x:c r="A184" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+      <x:c r="B184" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="C184" s="0" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="D184" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="185" spans="1:4">
+      <x:c r="A185" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="B185" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="C185" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D185" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="186" spans="1:4">
+      <x:c r="A186" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="B186" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="C186" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D186" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="187" spans="1:4">
+      <x:c r="A187" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B187" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="C187" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D187" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="188" spans="1:4">
+      <x:c r="A188" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="B188" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="C188" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D188" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="189" spans="1:4">
+      <x:c r="A189" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="B189" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+      <x:c r="C189" s="0" t="s">
+        <x:v>255</x:v>
+      </x:c>
+      <x:c r="D189" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="190" spans="1:4">
+      <x:c r="A190" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="B190" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="C190" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="D190" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="191" spans="1:4">
+      <x:c r="A191" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="B191" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="C191" s="0" t="s">
+        <x:v>10</x:v>
+      </x:c>
+      <x:c r="D191" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="192" spans="1:4">
+      <x:c r="A192" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+      <x:c r="B192" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="C192" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D192" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="193" spans="1:4">
+      <x:c r="A193" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="B193" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="C193" s="0" t="s">
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="D193" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="194" spans="1:4">
+      <x:c r="A194" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="B194" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="C194" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D194" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="195" spans="1:4">
+      <x:c r="A195" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B195" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="C195" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D195" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="196" spans="1:4">
+      <x:c r="A196" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="B196" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="C196" s="0" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D196" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="197" spans="1:4">
+      <x:c r="A197" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="B197" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+      <x:c r="C197" s="0" t="s">
+        <x:v>272</x:v>
+      </x:c>
+      <x:c r="D197" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="198" spans="1:4">
+      <x:c r="A198" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="B198" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="C198" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="D198" s="0" t="s">
+        <x:v>611</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
